--- a/099-納品物/000-要件定義/003-WBS-納品版.xlsx
+++ b/099-納品物/000-要件定義/003-WBS-納品版.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\099-納品物\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF3E516-3B5B-40F6-9BE9-BF4D39C2EBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DA2977-9474-469E-9183-BCA6C00CAC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2127,6 +2127,195 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2187,182 +2376,77 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2372,90 +2456,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3330,94 +3330,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="141" t="s">
+      <c r="B1" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="144" t="s">
+      <c r="C1" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="150" t="s">
+      <c r="D1" s="208"/>
+      <c r="E1" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="152" t="s">
+      <c r="F1" s="215" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="135">
+      <c r="G1" s="198">
         <v>45536</v>
       </c>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="136"/>
-      <c r="T1" s="136"/>
-      <c r="U1" s="136"/>
-      <c r="V1" s="136"/>
-      <c r="W1" s="136"/>
-      <c r="X1" s="136"/>
-      <c r="Y1" s="136"/>
-      <c r="Z1" s="136"/>
-      <c r="AA1" s="136"/>
-      <c r="AB1" s="136"/>
-      <c r="AC1" s="136"/>
-      <c r="AD1" s="136"/>
-      <c r="AE1" s="136"/>
-      <c r="AF1" s="136"/>
-      <c r="AG1" s="136"/>
-      <c r="AH1" s="136"/>
-      <c r="AI1" s="136"/>
-      <c r="AJ1" s="137"/>
-      <c r="AK1" s="135">
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="199"/>
+      <c r="O1" s="199"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="199"/>
+      <c r="Y1" s="199"/>
+      <c r="Z1" s="199"/>
+      <c r="AA1" s="199"/>
+      <c r="AB1" s="199"/>
+      <c r="AC1" s="199"/>
+      <c r="AD1" s="199"/>
+      <c r="AE1" s="199"/>
+      <c r="AF1" s="199"/>
+      <c r="AG1" s="199"/>
+      <c r="AH1" s="199"/>
+      <c r="AI1" s="199"/>
+      <c r="AJ1" s="200"/>
+      <c r="AK1" s="198">
         <v>45566</v>
       </c>
-      <c r="AL1" s="136"/>
-      <c r="AM1" s="136"/>
-      <c r="AN1" s="136"/>
-      <c r="AO1" s="136"/>
-      <c r="AP1" s="136"/>
-      <c r="AQ1" s="136"/>
-      <c r="AR1" s="136"/>
-      <c r="AS1" s="136"/>
-      <c r="AT1" s="136"/>
-      <c r="AU1" s="136"/>
-      <c r="AV1" s="136"/>
-      <c r="AW1" s="136"/>
-      <c r="AX1" s="136"/>
-      <c r="AY1" s="136"/>
-      <c r="AZ1" s="136"/>
-      <c r="BA1" s="136"/>
-      <c r="BB1" s="136"/>
-      <c r="BC1" s="136"/>
-      <c r="BD1" s="136"/>
-      <c r="BE1" s="136"/>
-      <c r="BF1" s="136"/>
-      <c r="BG1" s="136"/>
-      <c r="BH1" s="136"/>
-      <c r="BI1" s="136"/>
-      <c r="BJ1" s="136"/>
-      <c r="BK1" s="136"/>
-      <c r="BL1" s="136"/>
-      <c r="BM1" s="136"/>
-      <c r="BN1" s="137"/>
+      <c r="AL1" s="199"/>
+      <c r="AM1" s="199"/>
+      <c r="AN1" s="199"/>
+      <c r="AO1" s="199"/>
+      <c r="AP1" s="199"/>
+      <c r="AQ1" s="199"/>
+      <c r="AR1" s="199"/>
+      <c r="AS1" s="199"/>
+      <c r="AT1" s="199"/>
+      <c r="AU1" s="199"/>
+      <c r="AV1" s="199"/>
+      <c r="AW1" s="199"/>
+      <c r="AX1" s="199"/>
+      <c r="AY1" s="199"/>
+      <c r="AZ1" s="199"/>
+      <c r="BA1" s="199"/>
+      <c r="BB1" s="199"/>
+      <c r="BC1" s="199"/>
+      <c r="BD1" s="199"/>
+      <c r="BE1" s="199"/>
+      <c r="BF1" s="199"/>
+      <c r="BG1" s="199"/>
+      <c r="BH1" s="199"/>
+      <c r="BI1" s="199"/>
+      <c r="BJ1" s="199"/>
+      <c r="BK1" s="199"/>
+      <c r="BL1" s="199"/>
+      <c r="BM1" s="199"/>
+      <c r="BN1" s="200"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="139"/>
-      <c r="B2" s="142"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="153"/>
+      <c r="A2" s="202"/>
+      <c r="B2" s="205"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="216"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3659,12 +3659,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="140"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="148"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="154"/>
+      <c r="A3" s="203"/>
+      <c r="B3" s="206"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="217"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -3847,20 +3847,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="155">
+      <c r="A4" s="193">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="158"/>
-      <c r="E4" s="161" t="s">
+      <c r="D4" s="195"/>
+      <c r="E4" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="163"/>
+      <c r="F4" s="196"/>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -3923,12 +3923,12 @@
       <c r="BN4" s="71"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="156"/>
+      <c r="A5" s="163"/>
       <c r="B5" s="34"/>
       <c r="C5" s="159"/>
       <c r="D5" s="160"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="164"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="197"/>
       <c r="G5" s="122"/>
       <c r="H5" s="100"/>
       <c r="I5" s="123"/>
@@ -3991,18 +3991,18 @@
       <c r="BN5" s="119"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="165">
+      <c r="A6" s="149">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="173" t="s">
+      <c r="C6" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="174"/>
-      <c r="E6" s="177" t="s">
+      <c r="D6" s="158"/>
+      <c r="E6" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="178"/>
+      <c r="F6" s="189"/>
       <c r="G6" s="51"/>
       <c r="H6" s="62"/>
       <c r="I6" s="118"/>
@@ -4065,12 +4065,12 @@
       <c r="BN6" s="72"/>
     </row>
     <row r="7" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A7" s="156"/>
+      <c r="A7" s="163"/>
       <c r="B7" s="102"/>
       <c r="C7" s="175"/>
       <c r="D7" s="176"/>
-      <c r="E7" s="161"/>
-      <c r="F7" s="179"/>
+      <c r="E7" s="168"/>
+      <c r="F7" s="190"/>
       <c r="G7" s="101"/>
       <c r="H7" s="68"/>
       <c r="I7" s="96"/>
@@ -4133,20 +4133,20 @@
       <c r="BN7" s="72"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="165">
+      <c r="A8" s="149">
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="C8" s="184" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="161" t="s">
+      <c r="D8" s="185"/>
+      <c r="E8" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="205"/>
+      <c r="F8" s="153"/>
       <c r="G8" s="50"/>
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
@@ -4209,12 +4209,12 @@
       <c r="BN8" s="95"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="156"/>
+      <c r="A9" s="163"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="169"/>
-      <c r="E9" s="182"/>
-      <c r="F9" s="196"/>
+      <c r="C9" s="186"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="154"/>
       <c r="G9" s="51"/>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
@@ -4277,18 +4277,18 @@
       <c r="BN9" s="72"/>
     </row>
     <row r="10" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A10" s="165">
+      <c r="A10" s="149">
         <v>4</v>
       </c>
       <c r="B10" s="36"/>
-      <c r="C10" s="166" t="s">
+      <c r="C10" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="167"/>
-      <c r="E10" s="183" t="s">
+      <c r="D10" s="185"/>
+      <c r="E10" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="195"/>
+      <c r="F10" s="155"/>
       <c r="G10" s="51"/>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
@@ -4351,12 +4351,12 @@
       <c r="BN10" s="95"/>
     </row>
     <row r="11" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A11" s="156"/>
+      <c r="A11" s="163"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="168"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="162"/>
-      <c r="F11" s="196"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="154"/>
       <c r="G11" s="51"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -4419,18 +4419,18 @@
       <c r="BN11" s="72"/>
     </row>
     <row r="12" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A12" s="165">
+      <c r="A12" s="149">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="166" t="s">
+      <c r="C12" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="167"/>
-      <c r="E12" s="186" t="s">
+      <c r="D12" s="185"/>
+      <c r="E12" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="195"/>
+      <c r="F12" s="155"/>
       <c r="G12" s="51"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63"/>
@@ -4493,12 +4493,12 @@
       <c r="BN12" s="95"/>
     </row>
     <row r="13" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A13" s="156"/>
+      <c r="A13" s="163"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="180"/>
-      <c r="D13" s="181"/>
-      <c r="E13" s="183"/>
-      <c r="F13" s="203"/>
+      <c r="C13" s="191"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="152"/>
+      <c r="F13" s="156"/>
       <c r="G13" s="53"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
@@ -4561,20 +4561,20 @@
       <c r="BN13" s="127"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="165">
+      <c r="A14" s="149">
         <v>6</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="166" t="s">
+      <c r="C14" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="167"/>
-      <c r="E14" s="162" t="s">
+      <c r="D14" s="185"/>
+      <c r="E14" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="171"/>
+      <c r="F14" s="183"/>
       <c r="G14" s="50"/>
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
@@ -4637,12 +4637,12 @@
       <c r="BN14" s="95"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="156"/>
+      <c r="A15" s="163"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="168"/>
-      <c r="D15" s="169"/>
-      <c r="E15" s="170"/>
-      <c r="F15" s="172"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="174"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -4672,7 +4672,7 @@
       <c r="AG15" s="16"/>
       <c r="AH15" s="22"/>
       <c r="AI15" s="31"/>
-      <c r="AJ15" s="241"/>
+      <c r="AJ15" s="135"/>
       <c r="AK15" s="80"/>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
@@ -4705,18 +4705,18 @@
       <c r="BN15" s="126"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="165">
+      <c r="A16" s="149">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="173" t="s">
+      <c r="C16" s="157" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="174"/>
-      <c r="E16" s="186" t="s">
+      <c r="D16" s="158"/>
+      <c r="E16" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="187"/>
+      <c r="F16" s="173"/>
       <c r="G16" s="51"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -4779,12 +4779,12 @@
       <c r="BN16" s="95"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="156"/>
+      <c r="A17" s="163"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="184"/>
-      <c r="D17" s="185"/>
-      <c r="E17" s="183"/>
-      <c r="F17" s="171"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="183"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -4810,11 +4810,11 @@
       <c r="AC17" s="32"/>
       <c r="AD17" s="134"/>
       <c r="AE17" s="128"/>
-      <c r="AF17" s="242"/>
+      <c r="AF17" s="136"/>
       <c r="AG17" s="25"/>
       <c r="AH17" s="23"/>
       <c r="AI17" s="128"/>
-      <c r="AJ17" s="243"/>
+      <c r="AJ17" s="137"/>
       <c r="AK17" s="80"/>
       <c r="AL17" s="7"/>
       <c r="AM17" s="7"/>
@@ -4847,20 +4847,20 @@
       <c r="BN17" s="93"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="165">
+      <c r="A18" s="149">
         <v>8</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="188" t="s">
+      <c r="C18" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="189"/>
-      <c r="E18" s="161" t="s">
+      <c r="D18" s="144"/>
+      <c r="E18" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="190"/>
+      <c r="F18" s="178"/>
       <c r="G18" s="38"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
@@ -4923,12 +4923,12 @@
       <c r="BN18" s="133"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="156"/>
+      <c r="A19" s="163"/>
       <c r="B19" s="36"/>
       <c r="C19" s="159"/>
       <c r="D19" s="160"/>
-      <c r="E19" s="162"/>
-      <c r="F19" s="172"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="174"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -4959,7 +4959,7 @@
       <c r="AH19" s="26"/>
       <c r="AI19" s="117"/>
       <c r="AJ19" s="125"/>
-      <c r="AK19" s="244"/>
+      <c r="AK19" s="138"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="32"/>
       <c r="AN19" s="25"/>
@@ -4991,18 +4991,18 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="165">
+      <c r="A20" s="149">
         <v>9</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="173" t="s">
+      <c r="C20" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="174"/>
-      <c r="E20" s="177" t="s">
+      <c r="D20" s="158"/>
+      <c r="E20" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="187"/>
+      <c r="F20" s="173"/>
       <c r="G20" s="51"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -5065,12 +5065,12 @@
       <c r="BN20" s="95"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="156"/>
+      <c r="A21" s="163"/>
       <c r="B21" s="36"/>
       <c r="C21" s="159"/>
       <c r="D21" s="160"/>
-      <c r="E21" s="182"/>
-      <c r="F21" s="172"/>
+      <c r="E21" s="172"/>
+      <c r="F21" s="174"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -5106,9 +5106,9 @@
       <c r="AM21" s="32"/>
       <c r="AN21" s="25"/>
       <c r="AO21" s="26"/>
-      <c r="AP21" s="24"/>
-      <c r="AQ21" s="24"/>
-      <c r="AR21" s="24"/>
+      <c r="AP21" s="32"/>
+      <c r="AQ21" s="7"/>
+      <c r="AR21" s="7"/>
       <c r="AS21" s="24"/>
       <c r="AT21" s="24"/>
       <c r="AU21" s="25"/>
@@ -5133,18 +5133,18 @@
       <c r="BN21" s="72"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="165">
+      <c r="A22" s="149">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="173" t="s">
+      <c r="C22" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="174"/>
-      <c r="E22" s="183" t="s">
+      <c r="D22" s="158"/>
+      <c r="E22" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="187"/>
+      <c r="F22" s="173"/>
       <c r="G22" s="52"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -5207,12 +5207,12 @@
       <c r="BN22" s="95"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="156"/>
+      <c r="A23" s="163"/>
       <c r="B23" s="37"/>
       <c r="C23" s="175"/>
       <c r="D23" s="176"/>
-      <c r="E23" s="161"/>
-      <c r="F23" s="191"/>
+      <c r="E23" s="168"/>
+      <c r="F23" s="177"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5248,11 +5248,11 @@
       <c r="AM23" s="128"/>
       <c r="AN23" s="17"/>
       <c r="AO23" s="23"/>
-      <c r="AP23" s="68"/>
-      <c r="AQ23" s="68"/>
-      <c r="AR23" s="68"/>
-      <c r="AS23" s="68"/>
-      <c r="AT23" s="68"/>
+      <c r="AP23" s="64"/>
+      <c r="AQ23" s="128"/>
+      <c r="AR23" s="128"/>
+      <c r="AS23" s="128"/>
+      <c r="AT23" s="128"/>
       <c r="AU23" s="17"/>
       <c r="AV23" s="23"/>
       <c r="AW23" s="23"/>
@@ -5275,20 +5275,20 @@
       <c r="BN23" s="75"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="165">
+      <c r="A24" s="149">
         <v>11</v>
       </c>
-      <c r="B24" s="192" t="s">
+      <c r="B24" s="179" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="188" t="s">
+      <c r="C24" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="189"/>
-      <c r="E24" s="161" t="s">
+      <c r="D24" s="144"/>
+      <c r="E24" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="190"/>
+      <c r="F24" s="178"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5351,12 +5351,12 @@
       <c r="BN24" s="133"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="156"/>
-      <c r="B25" s="193"/>
+      <c r="A25" s="163"/>
+      <c r="B25" s="180"/>
       <c r="C25" s="159"/>
       <c r="D25" s="160"/>
-      <c r="E25" s="182"/>
-      <c r="F25" s="172"/>
+      <c r="E25" s="172"/>
+      <c r="F25" s="174"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5389,14 +5389,14 @@
       <c r="AJ25" s="77"/>
       <c r="AK25" s="87"/>
       <c r="AL25" s="63"/>
-      <c r="AM25" s="129"/>
+      <c r="AM25" s="63"/>
       <c r="AN25" s="13"/>
       <c r="AO25" s="19"/>
       <c r="AP25" s="110"/>
       <c r="AQ25" s="63"/>
       <c r="AR25" s="63"/>
       <c r="AS25" s="63"/>
-      <c r="AT25" s="63"/>
+      <c r="AT25" s="128"/>
       <c r="AU25" s="13"/>
       <c r="AV25" s="19"/>
       <c r="AW25" s="19"/>
@@ -5419,18 +5419,18 @@
       <c r="BN25" s="77"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="165">
+      <c r="A26" s="149">
         <v>12</v>
       </c>
-      <c r="B26" s="193"/>
-      <c r="C26" s="204" t="s">
+      <c r="B26" s="180"/>
+      <c r="C26" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="185"/>
-      <c r="E26" s="183" t="s">
+      <c r="D26" s="162"/>
+      <c r="E26" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="205"/>
+      <c r="F26" s="153"/>
       <c r="G26" s="50"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -5493,12 +5493,12 @@
       <c r="BN26" s="95"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="156"/>
-      <c r="B27" s="193"/>
+      <c r="A27" s="163"/>
+      <c r="B27" s="180"/>
       <c r="C27" s="159"/>
       <c r="D27" s="160"/>
-      <c r="E27" s="162"/>
-      <c r="F27" s="196"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="154"/>
       <c r="G27" s="51"/>
       <c r="H27" s="91"/>
       <c r="I27" s="7"/>
@@ -5561,18 +5561,18 @@
       <c r="BN27" s="77"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="165">
+      <c r="A28" s="149">
         <v>13</v>
       </c>
-      <c r="B28" s="193"/>
-      <c r="C28" s="173" t="s">
+      <c r="B28" s="180"/>
+      <c r="C28" s="157" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="174"/>
-      <c r="E28" s="177" t="s">
+      <c r="D28" s="158"/>
+      <c r="E28" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="195"/>
+      <c r="F28" s="155"/>
       <c r="G28" s="50"/>
       <c r="H28" s="9"/>
       <c r="I28" s="7"/>
@@ -5635,12 +5635,12 @@
       <c r="BN28" s="95"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="156"/>
-      <c r="B29" s="193"/>
+      <c r="A29" s="163"/>
+      <c r="B29" s="180"/>
       <c r="C29" s="159"/>
       <c r="D29" s="160"/>
-      <c r="E29" s="162"/>
-      <c r="F29" s="196"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="154"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="91"/>
@@ -5703,18 +5703,18 @@
       <c r="BN29" s="77"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="165">
+      <c r="A30" s="149">
         <v>14</v>
       </c>
-      <c r="B30" s="193"/>
-      <c r="C30" s="173" t="s">
+      <c r="B30" s="180"/>
+      <c r="C30" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="174"/>
-      <c r="E30" s="177" t="s">
+      <c r="D30" s="158"/>
+      <c r="E30" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F30" s="195"/>
+      <c r="F30" s="155"/>
       <c r="G30" s="50"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -5777,12 +5777,12 @@
       <c r="BN30" s="95"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="156"/>
-      <c r="B31" s="193"/>
+      <c r="A31" s="163"/>
+      <c r="B31" s="180"/>
       <c r="C31" s="159"/>
       <c r="D31" s="160"/>
-      <c r="E31" s="182"/>
-      <c r="F31" s="196"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="154"/>
       <c r="G31" s="51"/>
       <c r="H31" s="91"/>
       <c r="I31" s="7"/>
@@ -5845,18 +5845,18 @@
       <c r="BN31" s="77"/>
     </row>
     <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="165">
+      <c r="A32" s="149">
         <v>15</v>
       </c>
-      <c r="B32" s="193"/>
-      <c r="C32" s="173" t="s">
+      <c r="B32" s="180"/>
+      <c r="C32" s="157" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="174"/>
-      <c r="E32" s="183" t="s">
+      <c r="D32" s="158"/>
+      <c r="E32" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="195"/>
+      <c r="F32" s="155"/>
       <c r="G32" s="52"/>
       <c r="H32" s="24"/>
       <c r="I32" s="24"/>
@@ -5919,12 +5919,12 @@
       <c r="BN32" s="95"/>
     </row>
     <row r="33" spans="1:67" ht="12" customHeight="1">
-      <c r="A33" s="156"/>
-      <c r="B33" s="193"/>
+      <c r="A33" s="163"/>
+      <c r="B33" s="180"/>
       <c r="C33" s="159"/>
       <c r="D33" s="160"/>
-      <c r="E33" s="162"/>
-      <c r="F33" s="196"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="154"/>
       <c r="G33" s="52"/>
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
@@ -5987,18 +5987,18 @@
       <c r="BN33" s="77"/>
     </row>
     <row r="34" spans="1:67" ht="12" customHeight="1">
-      <c r="A34" s="165">
+      <c r="A34" s="149">
         <v>16</v>
       </c>
-      <c r="B34" s="193"/>
-      <c r="C34" s="173" t="s">
+      <c r="B34" s="180"/>
+      <c r="C34" s="157" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="174"/>
-      <c r="E34" s="177" t="s">
+      <c r="D34" s="158"/>
+      <c r="E34" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F34" s="195"/>
+      <c r="F34" s="155"/>
       <c r="G34" s="52"/>
       <c r="H34" s="24"/>
       <c r="I34" s="24"/>
@@ -6061,12 +6061,12 @@
       <c r="BN34" s="95"/>
     </row>
     <row r="35" spans="1:67" ht="12" customHeight="1">
-      <c r="A35" s="156"/>
-      <c r="B35" s="193"/>
+      <c r="A35" s="163"/>
+      <c r="B35" s="180"/>
       <c r="C35" s="159"/>
       <c r="D35" s="160"/>
-      <c r="E35" s="162"/>
-      <c r="F35" s="196"/>
+      <c r="E35" s="139"/>
+      <c r="F35" s="154"/>
       <c r="G35" s="52"/>
       <c r="H35" s="24"/>
       <c r="I35" s="24"/>
@@ -6129,18 +6129,18 @@
       <c r="BN35" s="77"/>
     </row>
     <row r="36" spans="1:67" ht="12" customHeight="1">
-      <c r="A36" s="165">
+      <c r="A36" s="149">
         <v>17</v>
       </c>
-      <c r="B36" s="193"/>
+      <c r="B36" s="180"/>
       <c r="C36" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D36" s="113"/>
-      <c r="E36" s="177" t="s">
+      <c r="E36" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="195"/>
+      <c r="F36" s="155"/>
       <c r="G36" s="52"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -6203,12 +6203,12 @@
       <c r="BN36" s="95"/>
     </row>
     <row r="37" spans="1:67" ht="12" customHeight="1">
-      <c r="A37" s="156"/>
-      <c r="B37" s="194"/>
+      <c r="A37" s="163"/>
+      <c r="B37" s="181"/>
       <c r="C37" s="114"/>
       <c r="D37" s="115"/>
-      <c r="E37" s="161"/>
-      <c r="F37" s="203"/>
+      <c r="E37" s="168"/>
+      <c r="F37" s="156"/>
       <c r="G37" s="54"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -6271,20 +6271,20 @@
       <c r="BN37" s="75"/>
     </row>
     <row r="38" spans="1:67" ht="12" customHeight="1">
-      <c r="A38" s="165">
+      <c r="A38" s="149">
         <v>20</v>
       </c>
       <c r="B38" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="197" t="s">
+      <c r="C38" s="164" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="198"/>
-      <c r="E38" s="161" t="s">
+      <c r="D38" s="165"/>
+      <c r="E38" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="201"/>
+      <c r="F38" s="169"/>
       <c r="G38" s="38"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -6348,12 +6348,12 @@
       <c r="BO38" s="97"/>
     </row>
     <row r="39" spans="1:67" ht="12" customHeight="1">
-      <c r="A39" s="156"/>
+      <c r="A39" s="163"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="199"/>
-      <c r="D39" s="200"/>
-      <c r="E39" s="161"/>
-      <c r="F39" s="202"/>
+      <c r="C39" s="166"/>
+      <c r="D39" s="167"/>
+      <c r="E39" s="168"/>
+      <c r="F39" s="170"/>
       <c r="G39" s="51"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -6417,20 +6417,20 @@
       <c r="BO39" s="97"/>
     </row>
     <row r="40" spans="1:67">
-      <c r="A40" s="165">
+      <c r="A40" s="149">
         <v>21</v>
       </c>
-      <c r="B40" s="207" t="s">
+      <c r="B40" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="188" t="s">
+      <c r="C40" s="143" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="189"/>
-      <c r="E40" s="162" t="s">
+      <c r="D40" s="144"/>
+      <c r="E40" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="F40" s="211"/>
+      <c r="F40" s="147"/>
       <c r="G40" s="38"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -6494,12 +6494,12 @@
       <c r="BO40" s="97"/>
     </row>
     <row r="41" spans="1:67" ht="10.199999999999999" thickBot="1">
-      <c r="A41" s="213"/>
-      <c r="B41" s="208"/>
-      <c r="C41" s="209"/>
-      <c r="D41" s="210"/>
-      <c r="E41" s="206"/>
-      <c r="F41" s="212"/>
+      <c r="A41" s="150"/>
+      <c r="B41" s="142"/>
+      <c r="C41" s="145"/>
+      <c r="D41" s="146"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="148"/>
       <c r="G41" s="39"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -6584,23 +6584,57 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B24:B37"/>
+    <mergeCell ref="F34:F35"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="C38:D39"/>
     <mergeCell ref="E38:E39"/>
@@ -6617,57 +6651,23 @@
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="E28:E29"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B24:B37"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="A40:A41"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -6703,54 +6703,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="141" t="s">
+      <c r="B1" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="144" t="s">
+      <c r="C1" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="150" t="s">
+      <c r="D1" s="208"/>
+      <c r="E1" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="152" t="s">
+      <c r="F1" s="215" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="135"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="136"/>
-      <c r="T1" s="136"/>
-      <c r="U1" s="136"/>
-      <c r="V1" s="136"/>
-      <c r="W1" s="136"/>
-      <c r="X1" s="136"/>
-      <c r="Y1" s="136"/>
-      <c r="Z1" s="136"/>
-      <c r="AA1" s="136"/>
-      <c r="AB1" s="136"/>
-      <c r="AC1" s="136"/>
-      <c r="AD1" s="137"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="199"/>
+      <c r="O1" s="199"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="199"/>
+      <c r="Y1" s="199"/>
+      <c r="Z1" s="199"/>
+      <c r="AA1" s="199"/>
+      <c r="AB1" s="199"/>
+      <c r="AC1" s="199"/>
+      <c r="AD1" s="200"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="139"/>
-      <c r="B2" s="142"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="153"/>
+      <c r="A2" s="202"/>
+      <c r="B2" s="205"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="216"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -6825,12 +6825,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="140"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="148"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="240"/>
-      <c r="F3" s="154"/>
+      <c r="A3" s="203"/>
+      <c r="B3" s="206"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="218"/>
+      <c r="F3" s="217"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -6905,20 +6905,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="155">
+      <c r="A4" s="193">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="158"/>
-      <c r="E4" s="233" t="s">
+      <c r="D4" s="195"/>
+      <c r="E4" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="163"/>
+      <c r="F4" s="196"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -6941,20 +6941,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="234" t="s">
+      <c r="AC4" s="225" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="228" t="s">
+      <c r="AD4" s="219" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="156"/>
+      <c r="A5" s="163"/>
       <c r="B5" s="34"/>
       <c r="C5" s="159"/>
       <c r="D5" s="160"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="164"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="197"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -6977,22 +6977,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="235"/>
-      <c r="AD5" s="229"/>
+      <c r="AC5" s="226"/>
+      <c r="AD5" s="220"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="165">
+      <c r="A6" s="149">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="173" t="s">
+      <c r="C6" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="174"/>
-      <c r="E6" s="231" t="s">
+      <c r="D6" s="158"/>
+      <c r="E6" s="222" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="178"/>
+      <c r="F6" s="189"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -7015,16 +7015,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="235"/>
-      <c r="AD6" s="229"/>
+      <c r="AC6" s="226"/>
+      <c r="AD6" s="220"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="156"/>
+      <c r="A7" s="163"/>
       <c r="B7" s="34"/>
       <c r="C7" s="175"/>
       <c r="D7" s="176"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="179"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="190"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -7047,24 +7047,24 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="235"/>
-      <c r="AD7" s="229"/>
+      <c r="AC7" s="226"/>
+      <c r="AD7" s="220"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="217">
+      <c r="A8" s="228">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="237" t="s">
+      <c r="C8" s="230" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="238"/>
-      <c r="E8" s="239" t="s">
+      <c r="D8" s="231"/>
+      <c r="E8" s="232" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="190"/>
+      <c r="F8" s="178"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -7087,16 +7087,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="235"/>
-      <c r="AD8" s="229"/>
+      <c r="AC8" s="226"/>
+      <c r="AD8" s="220"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="218"/>
+      <c r="A9" s="229"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="180"/>
-      <c r="D9" s="181"/>
-      <c r="E9" s="223"/>
-      <c r="F9" s="191"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="192"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="177"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -7119,24 +7119,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="235"/>
-      <c r="AD9" s="229"/>
+      <c r="AC9" s="226"/>
+      <c r="AD9" s="220"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="226">
+      <c r="A10" s="234">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="166" t="s">
+      <c r="C10" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="167"/>
-      <c r="E10" s="225" t="s">
+      <c r="D10" s="185"/>
+      <c r="E10" s="235" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="171"/>
+      <c r="F10" s="183"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -7159,16 +7159,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="235"/>
-      <c r="AD10" s="229"/>
+      <c r="AC10" s="226"/>
+      <c r="AD10" s="220"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="218"/>
+      <c r="A11" s="229"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="168"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="221"/>
-      <c r="F11" s="172"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="236"/>
+      <c r="F11" s="174"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -7191,22 +7191,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="235"/>
-      <c r="AD11" s="229"/>
+      <c r="AC11" s="226"/>
+      <c r="AD11" s="220"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="217">
+      <c r="A12" s="228">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="173" t="s">
+      <c r="C12" s="157" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="174"/>
-      <c r="E12" s="227" t="s">
+      <c r="D12" s="158"/>
+      <c r="E12" s="237" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="187"/>
+      <c r="F12" s="173"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7229,16 +7229,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="235"/>
-      <c r="AD12" s="229"/>
+      <c r="AC12" s="226"/>
+      <c r="AD12" s="220"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="226"/>
+      <c r="A13" s="234"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="184"/>
-      <c r="D13" s="185"/>
-      <c r="E13" s="225"/>
-      <c r="F13" s="171"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="162"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="183"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7261,24 +7261,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="235"/>
-      <c r="AD13" s="229"/>
+      <c r="AC13" s="226"/>
+      <c r="AD13" s="220"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="222">
+      <c r="A14" s="238">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="188" t="s">
+      <c r="C14" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="189"/>
-      <c r="E14" s="224" t="s">
+      <c r="D14" s="144"/>
+      <c r="E14" s="239" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="190"/>
+      <c r="F14" s="178"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7301,16 +7301,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="235"/>
-      <c r="AD14" s="229"/>
+      <c r="AC14" s="226"/>
+      <c r="AD14" s="220"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="222"/>
+      <c r="A15" s="238"/>
       <c r="B15" s="36"/>
       <c r="C15" s="159"/>
       <c r="D15" s="160"/>
-      <c r="E15" s="221"/>
-      <c r="F15" s="172"/>
+      <c r="E15" s="236"/>
+      <c r="F15" s="174"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7333,22 +7333,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="235"/>
-      <c r="AD15" s="229"/>
+      <c r="AC15" s="226"/>
+      <c r="AD15" s="220"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="222">
+      <c r="A16" s="238">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="173" t="s">
+      <c r="C16" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="174"/>
-      <c r="E16" s="220" t="s">
+      <c r="D16" s="158"/>
+      <c r="E16" s="240" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="187"/>
+      <c r="F16" s="173"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7371,16 +7371,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="235"/>
-      <c r="AD16" s="229"/>
+      <c r="AC16" s="226"/>
+      <c r="AD16" s="220"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="222"/>
+      <c r="A17" s="238"/>
       <c r="B17" s="36"/>
       <c r="C17" s="159"/>
       <c r="D17" s="160"/>
-      <c r="E17" s="221"/>
-      <c r="F17" s="172"/>
+      <c r="E17" s="236"/>
+      <c r="F17" s="174"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7403,22 +7403,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="235"/>
-      <c r="AD17" s="229"/>
+      <c r="AC17" s="226"/>
+      <c r="AD17" s="220"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="222">
+      <c r="A18" s="238">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="173" t="s">
+      <c r="C18" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="174"/>
-      <c r="E18" s="220" t="s">
+      <c r="D18" s="158"/>
+      <c r="E18" s="240" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="187"/>
+      <c r="F18" s="173"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7441,16 +7441,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="235"/>
-      <c r="AD18" s="229"/>
+      <c r="AC18" s="226"/>
+      <c r="AD18" s="220"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="222"/>
+      <c r="A19" s="238"/>
       <c r="B19" s="37"/>
       <c r="C19" s="175"/>
       <c r="D19" s="176"/>
-      <c r="E19" s="223"/>
-      <c r="F19" s="191"/>
+      <c r="E19" s="233"/>
+      <c r="F19" s="177"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7473,24 +7473,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="235"/>
-      <c r="AD19" s="229"/>
+      <c r="AC19" s="226"/>
+      <c r="AD19" s="220"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="217">
+      <c r="A20" s="228">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="188" t="s">
+      <c r="C20" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="189"/>
-      <c r="E20" s="224" t="s">
+      <c r="D20" s="144"/>
+      <c r="E20" s="239" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="190"/>
+      <c r="F20" s="178"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -7513,18 +7513,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="235"/>
-      <c r="AD20" s="229"/>
+      <c r="AC20" s="226"/>
+      <c r="AD20" s="220"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="218"/>
+      <c r="A21" s="229"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="159"/>
       <c r="D21" s="160"/>
-      <c r="E21" s="221"/>
-      <c r="F21" s="172"/>
+      <c r="E21" s="236"/>
+      <c r="F21" s="174"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -7547,22 +7547,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="235"/>
-      <c r="AD21" s="229"/>
+      <c r="AC21" s="226"/>
+      <c r="AD21" s="220"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="217">
+      <c r="A22" s="228">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="219" t="s">
+      <c r="C22" s="241" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="174"/>
-      <c r="E22" s="220" t="s">
+      <c r="D22" s="158"/>
+      <c r="E22" s="240" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="187"/>
+      <c r="F22" s="173"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -7585,16 +7585,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="235"/>
-      <c r="AD22" s="229"/>
+      <c r="AC22" s="226"/>
+      <c r="AD22" s="220"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="218"/>
+      <c r="A23" s="229"/>
       <c r="B23" s="36"/>
       <c r="C23" s="159"/>
       <c r="D23" s="160"/>
-      <c r="E23" s="221"/>
-      <c r="F23" s="172"/>
+      <c r="E23" s="236"/>
+      <c r="F23" s="174"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -7617,22 +7617,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="235"/>
-      <c r="AD23" s="229"/>
+      <c r="AC23" s="226"/>
+      <c r="AD23" s="220"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="217">
+      <c r="A24" s="228">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="219" t="s">
+      <c r="C24" s="241" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="174"/>
-      <c r="E24" s="220" t="s">
+      <c r="D24" s="158"/>
+      <c r="E24" s="240" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="187"/>
+      <c r="F24" s="173"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -7655,16 +7655,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="235"/>
-      <c r="AD24" s="229"/>
+      <c r="AC24" s="226"/>
+      <c r="AD24" s="220"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="218"/>
+      <c r="A25" s="229"/>
       <c r="B25" s="37"/>
       <c r="C25" s="159"/>
       <c r="D25" s="160"/>
-      <c r="E25" s="221"/>
-      <c r="F25" s="191"/>
+      <c r="E25" s="236"/>
+      <c r="F25" s="177"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7687,24 +7687,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="235"/>
-      <c r="AD25" s="229"/>
+      <c r="AC25" s="226"/>
+      <c r="AD25" s="220"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="165">
+      <c r="A26" s="149">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="197" t="s">
+      <c r="C26" s="164" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="198"/>
-      <c r="E26" s="214" t="s">
+      <c r="D26" s="165"/>
+      <c r="E26" s="242" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="201"/>
+      <c r="F26" s="169"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -7727,16 +7727,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="235"/>
-      <c r="AD26" s="229"/>
+      <c r="AC26" s="226"/>
+      <c r="AD26" s="220"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="156"/>
+      <c r="A27" s="163"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="199"/>
-      <c r="D27" s="200"/>
-      <c r="E27" s="215"/>
-      <c r="F27" s="202"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="167"/>
+      <c r="E27" s="243"/>
+      <c r="F27" s="170"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -7759,24 +7759,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="235"/>
-      <c r="AD27" s="229"/>
+      <c r="AC27" s="226"/>
+      <c r="AD27" s="220"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="165">
+      <c r="A28" s="149">
         <v>14</v>
       </c>
-      <c r="B28" s="207" t="s">
+      <c r="B28" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="188" t="s">
+      <c r="C28" s="143" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="189"/>
-      <c r="E28" s="207" t="s">
+      <c r="D28" s="144"/>
+      <c r="E28" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="211"/>
+      <c r="F28" s="147"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -7799,16 +7799,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="235"/>
-      <c r="AD28" s="229"/>
+      <c r="AC28" s="226"/>
+      <c r="AD28" s="220"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="216"/>
-      <c r="B29" s="208"/>
-      <c r="C29" s="209"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="208"/>
-      <c r="F29" s="212"/>
+      <c r="A29" s="244"/>
+      <c r="B29" s="142"/>
+      <c r="C29" s="145"/>
+      <c r="D29" s="146"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="148"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -7831,8 +7831,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="236"/>
-      <c r="AD29" s="230"/>
+      <c r="AC29" s="227"/>
+      <c r="AD29" s="221"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -7852,12 +7852,45 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -7874,45 +7907,12 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/099-納品物/000-要件定義/003-WBS-納品版.xlsx
+++ b/099-納品物/000-要件定義/003-WBS-納品版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\099-納品物\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DA2977-9474-469E-9183-BCA6C00CAC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBD7357-4B30-447E-B196-80DE91507450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体スケジュール" sheetId="13" r:id="rId1"/>
@@ -2139,9 +2139,219 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2151,12 +2361,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2169,293 +2373,89 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3330,94 +3330,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="204" t="s">
+      <c r="B1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="207" t="s">
+      <c r="C1" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="208"/>
-      <c r="E1" s="213" t="s">
+      <c r="D1" s="149"/>
+      <c r="E1" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="215" t="s">
+      <c r="F1" s="156" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="198">
+      <c r="G1" s="139">
         <v>45536</v>
       </c>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="199"/>
-      <c r="O1" s="199"/>
-      <c r="P1" s="199"/>
-      <c r="Q1" s="199"/>
-      <c r="R1" s="199"/>
-      <c r="S1" s="199"/>
-      <c r="T1" s="199"/>
-      <c r="U1" s="199"/>
-      <c r="V1" s="199"/>
-      <c r="W1" s="199"/>
-      <c r="X1" s="199"/>
-      <c r="Y1" s="199"/>
-      <c r="Z1" s="199"/>
-      <c r="AA1" s="199"/>
-      <c r="AB1" s="199"/>
-      <c r="AC1" s="199"/>
-      <c r="AD1" s="199"/>
-      <c r="AE1" s="199"/>
-      <c r="AF1" s="199"/>
-      <c r="AG1" s="199"/>
-      <c r="AH1" s="199"/>
-      <c r="AI1" s="199"/>
-      <c r="AJ1" s="200"/>
-      <c r="AK1" s="198">
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="140"/>
+      <c r="AA1" s="140"/>
+      <c r="AB1" s="140"/>
+      <c r="AC1" s="140"/>
+      <c r="AD1" s="140"/>
+      <c r="AE1" s="140"/>
+      <c r="AF1" s="140"/>
+      <c r="AG1" s="140"/>
+      <c r="AH1" s="140"/>
+      <c r="AI1" s="140"/>
+      <c r="AJ1" s="141"/>
+      <c r="AK1" s="139">
         <v>45566</v>
       </c>
-      <c r="AL1" s="199"/>
-      <c r="AM1" s="199"/>
-      <c r="AN1" s="199"/>
-      <c r="AO1" s="199"/>
-      <c r="AP1" s="199"/>
-      <c r="AQ1" s="199"/>
-      <c r="AR1" s="199"/>
-      <c r="AS1" s="199"/>
-      <c r="AT1" s="199"/>
-      <c r="AU1" s="199"/>
-      <c r="AV1" s="199"/>
-      <c r="AW1" s="199"/>
-      <c r="AX1" s="199"/>
-      <c r="AY1" s="199"/>
-      <c r="AZ1" s="199"/>
-      <c r="BA1" s="199"/>
-      <c r="BB1" s="199"/>
-      <c r="BC1" s="199"/>
-      <c r="BD1" s="199"/>
-      <c r="BE1" s="199"/>
-      <c r="BF1" s="199"/>
-      <c r="BG1" s="199"/>
-      <c r="BH1" s="199"/>
-      <c r="BI1" s="199"/>
-      <c r="BJ1" s="199"/>
-      <c r="BK1" s="199"/>
-      <c r="BL1" s="199"/>
-      <c r="BM1" s="199"/>
-      <c r="BN1" s="200"/>
+      <c r="AL1" s="140"/>
+      <c r="AM1" s="140"/>
+      <c r="AN1" s="140"/>
+      <c r="AO1" s="140"/>
+      <c r="AP1" s="140"/>
+      <c r="AQ1" s="140"/>
+      <c r="AR1" s="140"/>
+      <c r="AS1" s="140"/>
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="140"/>
+      <c r="BC1" s="140"/>
+      <c r="BD1" s="140"/>
+      <c r="BE1" s="140"/>
+      <c r="BF1" s="140"/>
+      <c r="BG1" s="140"/>
+      <c r="BH1" s="140"/>
+      <c r="BI1" s="140"/>
+      <c r="BJ1" s="140"/>
+      <c r="BK1" s="140"/>
+      <c r="BL1" s="140"/>
+      <c r="BM1" s="140"/>
+      <c r="BN1" s="141"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="202"/>
-      <c r="B2" s="205"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="216"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="157"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3659,12 +3659,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="203"/>
-      <c r="B3" s="206"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="214"/>
-      <c r="F3" s="217"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="152"/>
+      <c r="D3" s="153"/>
+      <c r="E3" s="155"/>
+      <c r="F3" s="158"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -3847,20 +3847,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="193">
+      <c r="A4" s="159">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="161" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="195"/>
-      <c r="E4" s="168" t="s">
+      <c r="D4" s="162"/>
+      <c r="E4" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="196"/>
+      <c r="F4" s="167"/>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -3923,12 +3923,12 @@
       <c r="BN4" s="71"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="163"/>
+      <c r="A5" s="160"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="197"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="164"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="168"/>
       <c r="G5" s="122"/>
       <c r="H5" s="100"/>
       <c r="I5" s="123"/>
@@ -3991,18 +3991,18 @@
       <c r="BN5" s="119"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="149">
+      <c r="A6" s="169">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="157" t="s">
+      <c r="C6" s="177" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="158"/>
-      <c r="E6" s="171" t="s">
+      <c r="D6" s="178"/>
+      <c r="E6" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="189"/>
+      <c r="F6" s="182"/>
       <c r="G6" s="51"/>
       <c r="H6" s="62"/>
       <c r="I6" s="118"/>
@@ -4065,12 +4065,12 @@
       <c r="BN6" s="72"/>
     </row>
     <row r="7" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A7" s="163"/>
+      <c r="A7" s="160"/>
       <c r="B7" s="102"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="168"/>
-      <c r="F7" s="190"/>
+      <c r="C7" s="179"/>
+      <c r="D7" s="180"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="183"/>
       <c r="G7" s="101"/>
       <c r="H7" s="68"/>
       <c r="I7" s="96"/>
@@ -4133,20 +4133,20 @@
       <c r="BN7" s="72"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="149">
+      <c r="A8" s="169">
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="184" t="s">
+      <c r="C8" s="170" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="185"/>
-      <c r="E8" s="168" t="s">
+      <c r="D8" s="171"/>
+      <c r="E8" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="153"/>
+      <c r="F8" s="209"/>
       <c r="G8" s="50"/>
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
@@ -4209,12 +4209,12 @@
       <c r="BN8" s="95"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="163"/>
+      <c r="A9" s="160"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="186"/>
-      <c r="D9" s="187"/>
-      <c r="E9" s="172"/>
-      <c r="F9" s="154"/>
+      <c r="C9" s="172"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="186"/>
+      <c r="F9" s="200"/>
       <c r="G9" s="51"/>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
@@ -4277,18 +4277,18 @@
       <c r="BN9" s="72"/>
     </row>
     <row r="10" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A10" s="149">
+      <c r="A10" s="169">
         <v>4</v>
       </c>
       <c r="B10" s="36"/>
-      <c r="C10" s="184" t="s">
+      <c r="C10" s="170" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="185"/>
-      <c r="E10" s="152" t="s">
+      <c r="D10" s="171"/>
+      <c r="E10" s="187" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="155"/>
+      <c r="F10" s="199"/>
       <c r="G10" s="51"/>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
@@ -4351,12 +4351,12 @@
       <c r="BN10" s="95"/>
     </row>
     <row r="11" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A11" s="163"/>
+      <c r="A11" s="160"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="154"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="200"/>
       <c r="G11" s="51"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -4419,18 +4419,18 @@
       <c r="BN11" s="72"/>
     </row>
     <row r="12" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A12" s="149">
+      <c r="A12" s="169">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="184" t="s">
+      <c r="C12" s="170" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="185"/>
-      <c r="E12" s="151" t="s">
+      <c r="D12" s="171"/>
+      <c r="E12" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="155"/>
+      <c r="F12" s="199"/>
       <c r="G12" s="51"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63"/>
@@ -4493,12 +4493,12 @@
       <c r="BN12" s="95"/>
     </row>
     <row r="13" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A13" s="163"/>
+      <c r="A13" s="160"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="191"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="156"/>
+      <c r="C13" s="184"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="187"/>
+      <c r="F13" s="207"/>
       <c r="G13" s="53"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
@@ -4561,20 +4561,20 @@
       <c r="BN13" s="127"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="149">
+      <c r="A14" s="169">
         <v>6</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="184" t="s">
+      <c r="C14" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="185"/>
-      <c r="E14" s="139" t="s">
+      <c r="D14" s="171"/>
+      <c r="E14" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="183"/>
+      <c r="F14" s="175"/>
       <c r="G14" s="50"/>
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
@@ -4637,12 +4637,12 @@
       <c r="BN14" s="95"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="163"/>
+      <c r="A15" s="160"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="187"/>
-      <c r="E15" s="188"/>
-      <c r="F15" s="174"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="174"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -4705,18 +4705,18 @@
       <c r="BN15" s="126"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="149">
+      <c r="A16" s="169">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="157" t="s">
+      <c r="C16" s="177" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="158"/>
-      <c r="E16" s="151" t="s">
+      <c r="D16" s="178"/>
+      <c r="E16" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="173"/>
+      <c r="F16" s="191"/>
       <c r="G16" s="51"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -4779,12 +4779,12 @@
       <c r="BN16" s="95"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="163"/>
+      <c r="A17" s="160"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="162"/>
-      <c r="E17" s="152"/>
-      <c r="F17" s="183"/>
+      <c r="C17" s="188"/>
+      <c r="D17" s="189"/>
+      <c r="E17" s="187"/>
+      <c r="F17" s="175"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -4847,20 +4847,20 @@
       <c r="BN17" s="93"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="149">
+      <c r="A18" s="169">
         <v>8</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="143" t="s">
+      <c r="C18" s="192" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="144"/>
-      <c r="E18" s="168" t="s">
+      <c r="D18" s="193"/>
+      <c r="E18" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="178"/>
+      <c r="F18" s="194"/>
       <c r="G18" s="38"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
@@ -4923,12 +4923,12 @@
       <c r="BN18" s="133"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="163"/>
+      <c r="A19" s="160"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="159"/>
-      <c r="D19" s="160"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="174"/>
+      <c r="C19" s="163"/>
+      <c r="D19" s="164"/>
+      <c r="E19" s="166"/>
+      <c r="F19" s="176"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -4991,18 +4991,18 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="149">
+      <c r="A20" s="169">
         <v>9</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="157" t="s">
+      <c r="C20" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="158"/>
-      <c r="E20" s="171" t="s">
+      <c r="D20" s="178"/>
+      <c r="E20" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="173"/>
+      <c r="F20" s="191"/>
       <c r="G20" s="51"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -5065,12 +5065,12 @@
       <c r="BN20" s="95"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="163"/>
+      <c r="A21" s="160"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="159"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="174"/>
+      <c r="C21" s="163"/>
+      <c r="D21" s="164"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -5133,18 +5133,18 @@
       <c r="BN21" s="72"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="149">
+      <c r="A22" s="169">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="157" t="s">
+      <c r="C22" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="158"/>
-      <c r="E22" s="152" t="s">
+      <c r="D22" s="178"/>
+      <c r="E22" s="187" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="173"/>
+      <c r="F22" s="191"/>
       <c r="G22" s="52"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -5207,12 +5207,12 @@
       <c r="BN22" s="95"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="163"/>
+      <c r="A23" s="160"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="176"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="177"/>
+      <c r="C23" s="179"/>
+      <c r="D23" s="180"/>
+      <c r="E23" s="165"/>
+      <c r="F23" s="195"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5275,20 +5275,20 @@
       <c r="BN23" s="75"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="149">
+      <c r="A24" s="169">
         <v>11</v>
       </c>
-      <c r="B24" s="179" t="s">
+      <c r="B24" s="196" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="143" t="s">
+      <c r="C24" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="144"/>
-      <c r="E24" s="168" t="s">
+      <c r="D24" s="193"/>
+      <c r="E24" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="178"/>
+      <c r="F24" s="194"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5351,12 +5351,12 @@
       <c r="BN24" s="133"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="163"/>
-      <c r="B25" s="180"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="172"/>
-      <c r="F25" s="174"/>
+      <c r="A25" s="160"/>
+      <c r="B25" s="197"/>
+      <c r="C25" s="163"/>
+      <c r="D25" s="164"/>
+      <c r="E25" s="186"/>
+      <c r="F25" s="176"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5419,18 +5419,18 @@
       <c r="BN25" s="77"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="149">
+      <c r="A26" s="169">
         <v>12</v>
       </c>
-      <c r="B26" s="180"/>
-      <c r="C26" s="161" t="s">
+      <c r="B26" s="197"/>
+      <c r="C26" s="208" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="162"/>
-      <c r="E26" s="152" t="s">
+      <c r="D26" s="189"/>
+      <c r="E26" s="187" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="153"/>
+      <c r="F26" s="209"/>
       <c r="G26" s="50"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -5493,12 +5493,12 @@
       <c r="BN26" s="95"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="163"/>
-      <c r="B27" s="180"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="160"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="154"/>
+      <c r="A27" s="160"/>
+      <c r="B27" s="197"/>
+      <c r="C27" s="163"/>
+      <c r="D27" s="164"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="200"/>
       <c r="G27" s="51"/>
       <c r="H27" s="91"/>
       <c r="I27" s="7"/>
@@ -5542,13 +5542,13 @@
       <c r="AU27" s="13"/>
       <c r="AV27" s="19"/>
       <c r="AW27" s="19"/>
-      <c r="AX27" s="63"/>
-      <c r="AY27" s="63"/>
-      <c r="AZ27" s="63"/>
-      <c r="BA27" s="63"/>
+      <c r="AX27" s="129"/>
+      <c r="AY27" s="129"/>
+      <c r="AZ27" s="129"/>
+      <c r="BA27" s="129"/>
       <c r="BB27" s="13"/>
       <c r="BC27" s="19"/>
-      <c r="BD27" s="63"/>
+      <c r="BD27" s="62"/>
       <c r="BE27" s="63"/>
       <c r="BF27" s="63"/>
       <c r="BG27" s="63"/>
@@ -5561,18 +5561,18 @@
       <c r="BN27" s="77"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="149">
+      <c r="A28" s="169">
         <v>13</v>
       </c>
-      <c r="B28" s="180"/>
-      <c r="C28" s="157" t="s">
+      <c r="B28" s="197"/>
+      <c r="C28" s="177" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="158"/>
-      <c r="E28" s="171" t="s">
+      <c r="D28" s="178"/>
+      <c r="E28" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="155"/>
+      <c r="F28" s="199"/>
       <c r="G28" s="50"/>
       <c r="H28" s="9"/>
       <c r="I28" s="7"/>
@@ -5622,7 +5622,7 @@
       <c r="BA28" s="63"/>
       <c r="BB28" s="13"/>
       <c r="BC28" s="19"/>
-      <c r="BD28" s="63"/>
+      <c r="BD28" s="62"/>
       <c r="BE28" s="63"/>
       <c r="BF28" s="63"/>
       <c r="BG28" s="63"/>
@@ -5635,12 +5635,12 @@
       <c r="BN28" s="95"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="163"/>
-      <c r="B29" s="180"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="160"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="154"/>
+      <c r="A29" s="160"/>
+      <c r="B29" s="197"/>
+      <c r="C29" s="163"/>
+      <c r="D29" s="164"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="200"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="91"/>
@@ -5686,11 +5686,11 @@
       <c r="AW29" s="19"/>
       <c r="AX29" s="63"/>
       <c r="AY29" s="63"/>
-      <c r="AZ29" s="63"/>
-      <c r="BA29" s="63"/>
+      <c r="AZ29" s="129"/>
+      <c r="BA29" s="129"/>
       <c r="BB29" s="13"/>
       <c r="BC29" s="19"/>
-      <c r="BD29" s="63"/>
+      <c r="BD29" s="62"/>
       <c r="BE29" s="63"/>
       <c r="BF29" s="63"/>
       <c r="BG29" s="63"/>
@@ -5703,18 +5703,18 @@
       <c r="BN29" s="77"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="149">
+      <c r="A30" s="169">
         <v>14</v>
       </c>
-      <c r="B30" s="180"/>
-      <c r="C30" s="157" t="s">
+      <c r="B30" s="197"/>
+      <c r="C30" s="177" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="158"/>
-      <c r="E30" s="171" t="s">
+      <c r="D30" s="178"/>
+      <c r="E30" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="F30" s="155"/>
+      <c r="F30" s="199"/>
       <c r="G30" s="50"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -5764,7 +5764,7 @@
       <c r="BA30" s="63"/>
       <c r="BB30" s="13"/>
       <c r="BC30" s="19"/>
-      <c r="BD30" s="63"/>
+      <c r="BD30" s="62"/>
       <c r="BE30" s="63"/>
       <c r="BF30" s="63"/>
       <c r="BG30" s="63"/>
@@ -5777,12 +5777,12 @@
       <c r="BN30" s="95"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="163"/>
-      <c r="B31" s="180"/>
-      <c r="C31" s="159"/>
-      <c r="D31" s="160"/>
-      <c r="E31" s="172"/>
-      <c r="F31" s="154"/>
+      <c r="A31" s="160"/>
+      <c r="B31" s="197"/>
+      <c r="C31" s="163"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="200"/>
       <c r="G31" s="51"/>
       <c r="H31" s="91"/>
       <c r="I31" s="7"/>
@@ -5845,18 +5845,18 @@
       <c r="BN31" s="77"/>
     </row>
     <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="149">
+      <c r="A32" s="169">
         <v>15</v>
       </c>
-      <c r="B32" s="180"/>
-      <c r="C32" s="157" t="s">
+      <c r="B32" s="197"/>
+      <c r="C32" s="177" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="158"/>
-      <c r="E32" s="152" t="s">
+      <c r="D32" s="178"/>
+      <c r="E32" s="187" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="155"/>
+      <c r="F32" s="199"/>
       <c r="G32" s="52"/>
       <c r="H32" s="24"/>
       <c r="I32" s="24"/>
@@ -5919,12 +5919,12 @@
       <c r="BN32" s="95"/>
     </row>
     <row r="33" spans="1:67" ht="12" customHeight="1">
-      <c r="A33" s="163"/>
-      <c r="B33" s="180"/>
-      <c r="C33" s="159"/>
-      <c r="D33" s="160"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="154"/>
+      <c r="A33" s="160"/>
+      <c r="B33" s="197"/>
+      <c r="C33" s="163"/>
+      <c r="D33" s="164"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="200"/>
       <c r="G33" s="52"/>
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
@@ -5987,18 +5987,18 @@
       <c r="BN33" s="77"/>
     </row>
     <row r="34" spans="1:67" ht="12" customHeight="1">
-      <c r="A34" s="149">
+      <c r="A34" s="169">
         <v>16</v>
       </c>
-      <c r="B34" s="180"/>
-      <c r="C34" s="157" t="s">
+      <c r="B34" s="197"/>
+      <c r="C34" s="177" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="158"/>
-      <c r="E34" s="171" t="s">
+      <c r="D34" s="178"/>
+      <c r="E34" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="F34" s="155"/>
+      <c r="F34" s="199"/>
       <c r="G34" s="52"/>
       <c r="H34" s="24"/>
       <c r="I34" s="24"/>
@@ -6061,12 +6061,12 @@
       <c r="BN34" s="95"/>
     </row>
     <row r="35" spans="1:67" ht="12" customHeight="1">
-      <c r="A35" s="163"/>
-      <c r="B35" s="180"/>
-      <c r="C35" s="159"/>
-      <c r="D35" s="160"/>
-      <c r="E35" s="139"/>
-      <c r="F35" s="154"/>
+      <c r="A35" s="160"/>
+      <c r="B35" s="197"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="164"/>
+      <c r="E35" s="166"/>
+      <c r="F35" s="200"/>
       <c r="G35" s="52"/>
       <c r="H35" s="24"/>
       <c r="I35" s="24"/>
@@ -6129,18 +6129,18 @@
       <c r="BN35" s="77"/>
     </row>
     <row r="36" spans="1:67" ht="12" customHeight="1">
-      <c r="A36" s="149">
+      <c r="A36" s="169">
         <v>17</v>
       </c>
-      <c r="B36" s="180"/>
+      <c r="B36" s="197"/>
       <c r="C36" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D36" s="113"/>
-      <c r="E36" s="171" t="s">
+      <c r="E36" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="155"/>
+      <c r="F36" s="199"/>
       <c r="G36" s="52"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -6203,12 +6203,12 @@
       <c r="BN36" s="95"/>
     </row>
     <row r="37" spans="1:67" ht="12" customHeight="1">
-      <c r="A37" s="163"/>
-      <c r="B37" s="181"/>
+      <c r="A37" s="160"/>
+      <c r="B37" s="198"/>
       <c r="C37" s="114"/>
       <c r="D37" s="115"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="156"/>
+      <c r="E37" s="165"/>
+      <c r="F37" s="207"/>
       <c r="G37" s="54"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -6271,20 +6271,20 @@
       <c r="BN37" s="75"/>
     </row>
     <row r="38" spans="1:67" ht="12" customHeight="1">
-      <c r="A38" s="149">
+      <c r="A38" s="169">
         <v>20</v>
       </c>
       <c r="B38" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="164" t="s">
+      <c r="C38" s="201" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="165"/>
-      <c r="E38" s="168" t="s">
+      <c r="D38" s="202"/>
+      <c r="E38" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="169"/>
+      <c r="F38" s="205"/>
       <c r="G38" s="38"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -6348,12 +6348,12 @@
       <c r="BO38" s="97"/>
     </row>
     <row r="39" spans="1:67" ht="12" customHeight="1">
-      <c r="A39" s="163"/>
+      <c r="A39" s="160"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="166"/>
-      <c r="D39" s="167"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="170"/>
+      <c r="C39" s="203"/>
+      <c r="D39" s="204"/>
+      <c r="E39" s="165"/>
+      <c r="F39" s="206"/>
       <c r="G39" s="51"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -6417,20 +6417,20 @@
       <c r="BO39" s="97"/>
     </row>
     <row r="40" spans="1:67">
-      <c r="A40" s="149">
+      <c r="A40" s="169">
         <v>21</v>
       </c>
-      <c r="B40" s="141" t="s">
+      <c r="B40" s="211" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="143" t="s">
+      <c r="C40" s="192" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="144"/>
-      <c r="E40" s="139" t="s">
+      <c r="D40" s="193"/>
+      <c r="E40" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="F40" s="147"/>
+      <c r="F40" s="215"/>
       <c r="G40" s="38"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -6494,12 +6494,12 @@
       <c r="BO40" s="97"/>
     </row>
     <row r="41" spans="1:67" ht="10.199999999999999" thickBot="1">
-      <c r="A41" s="150"/>
-      <c r="B41" s="142"/>
-      <c r="C41" s="145"/>
-      <c r="D41" s="146"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="148"/>
+      <c r="A41" s="217"/>
+      <c r="B41" s="212"/>
+      <c r="C41" s="213"/>
+      <c r="D41" s="214"/>
+      <c r="E41" s="210"/>
+      <c r="F41" s="216"/>
       <c r="G41" s="39"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -6584,17 +6584,63 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="C32:D33"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B24:B37"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="C14:D15"/>
     <mergeCell ref="E14:E15"/>
@@ -6611,63 +6657,17 @@
     <mergeCell ref="C12:D13"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B24:B37"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -6703,54 +6703,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="204" t="s">
+      <c r="B1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="207" t="s">
+      <c r="C1" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="208"/>
-      <c r="E1" s="213" t="s">
+      <c r="D1" s="149"/>
+      <c r="E1" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="215" t="s">
+      <c r="F1" s="156" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="198"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="199"/>
-      <c r="O1" s="199"/>
-      <c r="P1" s="199"/>
-      <c r="Q1" s="199"/>
-      <c r="R1" s="199"/>
-      <c r="S1" s="199"/>
-      <c r="T1" s="199"/>
-      <c r="U1" s="199"/>
-      <c r="V1" s="199"/>
-      <c r="W1" s="199"/>
-      <c r="X1" s="199"/>
-      <c r="Y1" s="199"/>
-      <c r="Z1" s="199"/>
-      <c r="AA1" s="199"/>
-      <c r="AB1" s="199"/>
-      <c r="AC1" s="199"/>
-      <c r="AD1" s="200"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
+      <c r="Z1" s="140"/>
+      <c r="AA1" s="140"/>
+      <c r="AB1" s="140"/>
+      <c r="AC1" s="140"/>
+      <c r="AD1" s="141"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="202"/>
-      <c r="B2" s="205"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="216"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="157"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -6825,12 +6825,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="203"/>
-      <c r="B3" s="206"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="217"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="152"/>
+      <c r="D3" s="153"/>
+      <c r="E3" s="244"/>
+      <c r="F3" s="158"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -6905,20 +6905,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="193">
+      <c r="A4" s="159">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="161" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="195"/>
-      <c r="E4" s="224" t="s">
+      <c r="D4" s="162"/>
+      <c r="E4" s="237" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="196"/>
+      <c r="F4" s="167"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -6941,20 +6941,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="225" t="s">
+      <c r="AC4" s="238" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="219" t="s">
+      <c r="AD4" s="232" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="163"/>
+      <c r="A5" s="160"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="197"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="164"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="168"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -6977,22 +6977,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="226"/>
-      <c r="AD5" s="220"/>
+      <c r="AC5" s="239"/>
+      <c r="AD5" s="233"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="149">
+      <c r="A6" s="169">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="157" t="s">
+      <c r="C6" s="177" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="158"/>
-      <c r="E6" s="222" t="s">
+      <c r="D6" s="178"/>
+      <c r="E6" s="235" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="189"/>
+      <c r="F6" s="182"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -7015,16 +7015,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="226"/>
-      <c r="AD6" s="220"/>
+      <c r="AC6" s="239"/>
+      <c r="AD6" s="233"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="163"/>
+      <c r="A7" s="160"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="190"/>
+      <c r="C7" s="179"/>
+      <c r="D7" s="180"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="183"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -7047,24 +7047,24 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="226"/>
-      <c r="AD7" s="220"/>
+      <c r="AC7" s="239"/>
+      <c r="AD7" s="233"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="228">
+      <c r="A8" s="221">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="230" t="s">
+      <c r="C8" s="241" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="231"/>
-      <c r="E8" s="232" t="s">
+      <c r="D8" s="242"/>
+      <c r="E8" s="243" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="178"/>
+      <c r="F8" s="194"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -7087,16 +7087,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="226"/>
-      <c r="AD8" s="220"/>
+      <c r="AC8" s="239"/>
+      <c r="AD8" s="233"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="229"/>
+      <c r="A9" s="222"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="191"/>
-      <c r="D9" s="192"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="177"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="185"/>
+      <c r="E9" s="227"/>
+      <c r="F9" s="195"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -7119,24 +7119,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="226"/>
-      <c r="AD9" s="220"/>
+      <c r="AC9" s="239"/>
+      <c r="AD9" s="233"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="234">
+      <c r="A10" s="230">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="184" t="s">
+      <c r="C10" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="185"/>
-      <c r="E10" s="235" t="s">
+      <c r="D10" s="171"/>
+      <c r="E10" s="229" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="183"/>
+      <c r="F10" s="175"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -7159,16 +7159,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="226"/>
-      <c r="AD10" s="220"/>
+      <c r="AC10" s="239"/>
+      <c r="AD10" s="233"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="229"/>
+      <c r="A11" s="222"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="174"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="225"/>
+      <c r="F11" s="176"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -7191,22 +7191,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="226"/>
-      <c r="AD11" s="220"/>
+      <c r="AC11" s="239"/>
+      <c r="AD11" s="233"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="228">
+      <c r="A12" s="221">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="157" t="s">
+      <c r="C12" s="177" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="158"/>
-      <c r="E12" s="237" t="s">
+      <c r="D12" s="178"/>
+      <c r="E12" s="231" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="173"/>
+      <c r="F12" s="191"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7229,16 +7229,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="226"/>
-      <c r="AD12" s="220"/>
+      <c r="AC12" s="239"/>
+      <c r="AD12" s="233"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="234"/>
+      <c r="A13" s="230"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="182"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="183"/>
+      <c r="C13" s="188"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="229"/>
+      <c r="F13" s="175"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7261,24 +7261,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="226"/>
-      <c r="AD13" s="220"/>
+      <c r="AC13" s="239"/>
+      <c r="AD13" s="233"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="238">
+      <c r="A14" s="226">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="143" t="s">
+      <c r="C14" s="192" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="239" t="s">
+      <c r="D14" s="193"/>
+      <c r="E14" s="228" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="178"/>
+      <c r="F14" s="194"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7301,16 +7301,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="226"/>
-      <c r="AD14" s="220"/>
+      <c r="AC14" s="239"/>
+      <c r="AD14" s="233"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="238"/>
+      <c r="A15" s="226"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="159"/>
-      <c r="D15" s="160"/>
-      <c r="E15" s="236"/>
-      <c r="F15" s="174"/>
+      <c r="C15" s="163"/>
+      <c r="D15" s="164"/>
+      <c r="E15" s="225"/>
+      <c r="F15" s="176"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7333,22 +7333,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="226"/>
-      <c r="AD15" s="220"/>
+      <c r="AC15" s="239"/>
+      <c r="AD15" s="233"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="238">
+      <c r="A16" s="226">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="157" t="s">
+      <c r="C16" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="158"/>
-      <c r="E16" s="240" t="s">
+      <c r="D16" s="178"/>
+      <c r="E16" s="224" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="173"/>
+      <c r="F16" s="191"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7371,16 +7371,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="226"/>
-      <c r="AD16" s="220"/>
+      <c r="AC16" s="239"/>
+      <c r="AD16" s="233"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="238"/>
+      <c r="A17" s="226"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="159"/>
-      <c r="D17" s="160"/>
-      <c r="E17" s="236"/>
-      <c r="F17" s="174"/>
+      <c r="C17" s="163"/>
+      <c r="D17" s="164"/>
+      <c r="E17" s="225"/>
+      <c r="F17" s="176"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7403,22 +7403,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="226"/>
-      <c r="AD17" s="220"/>
+      <c r="AC17" s="239"/>
+      <c r="AD17" s="233"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="238">
+      <c r="A18" s="226">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="157" t="s">
+      <c r="C18" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="158"/>
-      <c r="E18" s="240" t="s">
+      <c r="D18" s="178"/>
+      <c r="E18" s="224" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="173"/>
+      <c r="F18" s="191"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7441,16 +7441,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="226"/>
-      <c r="AD18" s="220"/>
+      <c r="AC18" s="239"/>
+      <c r="AD18" s="233"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="238"/>
+      <c r="A19" s="226"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="233"/>
-      <c r="F19" s="177"/>
+      <c r="C19" s="179"/>
+      <c r="D19" s="180"/>
+      <c r="E19" s="227"/>
+      <c r="F19" s="195"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7473,24 +7473,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="226"/>
-      <c r="AD19" s="220"/>
+      <c r="AC19" s="239"/>
+      <c r="AD19" s="233"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="228">
+      <c r="A20" s="221">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="143" t="s">
+      <c r="C20" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="144"/>
-      <c r="E20" s="239" t="s">
+      <c r="D20" s="193"/>
+      <c r="E20" s="228" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="178"/>
+      <c r="F20" s="194"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -7513,18 +7513,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="226"/>
-      <c r="AD20" s="220"/>
+      <c r="AC20" s="239"/>
+      <c r="AD20" s="233"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="229"/>
+      <c r="A21" s="222"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="159"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="236"/>
-      <c r="F21" s="174"/>
+      <c r="C21" s="163"/>
+      <c r="D21" s="164"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="176"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -7547,22 +7547,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="226"/>
-      <c r="AD21" s="220"/>
+      <c r="AC21" s="239"/>
+      <c r="AD21" s="233"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="228">
+      <c r="A22" s="221">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="241" t="s">
+      <c r="C22" s="223" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="158"/>
-      <c r="E22" s="240" t="s">
+      <c r="D22" s="178"/>
+      <c r="E22" s="224" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="173"/>
+      <c r="F22" s="191"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -7585,16 +7585,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="226"/>
-      <c r="AD22" s="220"/>
+      <c r="AC22" s="239"/>
+      <c r="AD22" s="233"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="229"/>
+      <c r="A23" s="222"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="159"/>
-      <c r="D23" s="160"/>
-      <c r="E23" s="236"/>
-      <c r="F23" s="174"/>
+      <c r="C23" s="163"/>
+      <c r="D23" s="164"/>
+      <c r="E23" s="225"/>
+      <c r="F23" s="176"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -7617,22 +7617,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="226"/>
-      <c r="AD23" s="220"/>
+      <c r="AC23" s="239"/>
+      <c r="AD23" s="233"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="228">
+      <c r="A24" s="221">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="241" t="s">
+      <c r="C24" s="223" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="158"/>
-      <c r="E24" s="240" t="s">
+      <c r="D24" s="178"/>
+      <c r="E24" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="173"/>
+      <c r="F24" s="191"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -7655,16 +7655,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="226"/>
-      <c r="AD24" s="220"/>
+      <c r="AC24" s="239"/>
+      <c r="AD24" s="233"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="229"/>
+      <c r="A25" s="222"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="236"/>
-      <c r="F25" s="177"/>
+      <c r="C25" s="163"/>
+      <c r="D25" s="164"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="195"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7687,24 +7687,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="226"/>
-      <c r="AD25" s="220"/>
+      <c r="AC25" s="239"/>
+      <c r="AD25" s="233"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="149">
+      <c r="A26" s="169">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="164" t="s">
+      <c r="C26" s="201" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="165"/>
-      <c r="E26" s="242" t="s">
+      <c r="D26" s="202"/>
+      <c r="E26" s="218" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="169"/>
+      <c r="F26" s="205"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -7727,16 +7727,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="226"/>
-      <c r="AD26" s="220"/>
+      <c r="AC26" s="239"/>
+      <c r="AD26" s="233"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="163"/>
+      <c r="A27" s="160"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="166"/>
-      <c r="D27" s="167"/>
-      <c r="E27" s="243"/>
-      <c r="F27" s="170"/>
+      <c r="C27" s="203"/>
+      <c r="D27" s="204"/>
+      <c r="E27" s="219"/>
+      <c r="F27" s="206"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -7759,24 +7759,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="226"/>
-      <c r="AD27" s="220"/>
+      <c r="AC27" s="239"/>
+      <c r="AD27" s="233"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="149">
+      <c r="A28" s="169">
         <v>14</v>
       </c>
-      <c r="B28" s="141" t="s">
+      <c r="B28" s="211" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="143" t="s">
+      <c r="C28" s="192" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="144"/>
-      <c r="E28" s="141" t="s">
+      <c r="D28" s="193"/>
+      <c r="E28" s="211" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="147"/>
+      <c r="F28" s="215"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -7799,16 +7799,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="226"/>
-      <c r="AD28" s="220"/>
+      <c r="AC28" s="239"/>
+      <c r="AD28" s="233"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="244"/>
-      <c r="B29" s="142"/>
-      <c r="C29" s="145"/>
-      <c r="D29" s="146"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="148"/>
+      <c r="A29" s="220"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="213"/>
+      <c r="D29" s="214"/>
+      <c r="E29" s="212"/>
+      <c r="F29" s="216"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -7831,8 +7831,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="227"/>
-      <c r="AD29" s="221"/>
+      <c r="AC29" s="240"/>
+      <c r="AD29" s="234"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -7852,45 +7852,12 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -7907,12 +7874,45 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/099-納品物/000-要件定義/003-WBS-納品版.xlsx
+++ b/099-納品物/000-要件定義/003-WBS-納品版.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\099-納品物\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBD7357-4B30-447E-B196-80DE91507450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6636C90D-2BE2-4AE9-9C4D-C0FBAECBABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1735,7 +1735,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2139,6 +2139,183 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2199,182 +2376,77 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2385,77 +2457,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3330,94 +3333,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="145" t="s">
+      <c r="B1" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="149"/>
-      <c r="E1" s="154" t="s">
+      <c r="D1" s="208"/>
+      <c r="E1" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="215" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="139">
+      <c r="G1" s="198">
         <v>45536</v>
       </c>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="140"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="140"/>
-      <c r="AD1" s="140"/>
-      <c r="AE1" s="140"/>
-      <c r="AF1" s="140"/>
-      <c r="AG1" s="140"/>
-      <c r="AH1" s="140"/>
-      <c r="AI1" s="140"/>
-      <c r="AJ1" s="141"/>
-      <c r="AK1" s="139">
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="199"/>
+      <c r="O1" s="199"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="199"/>
+      <c r="Y1" s="199"/>
+      <c r="Z1" s="199"/>
+      <c r="AA1" s="199"/>
+      <c r="AB1" s="199"/>
+      <c r="AC1" s="199"/>
+      <c r="AD1" s="199"/>
+      <c r="AE1" s="199"/>
+      <c r="AF1" s="199"/>
+      <c r="AG1" s="199"/>
+      <c r="AH1" s="199"/>
+      <c r="AI1" s="199"/>
+      <c r="AJ1" s="200"/>
+      <c r="AK1" s="198">
         <v>45566</v>
       </c>
-      <c r="AL1" s="140"/>
-      <c r="AM1" s="140"/>
-      <c r="AN1" s="140"/>
-      <c r="AO1" s="140"/>
-      <c r="AP1" s="140"/>
-      <c r="AQ1" s="140"/>
-      <c r="AR1" s="140"/>
-      <c r="AS1" s="140"/>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="140"/>
-      <c r="BC1" s="140"/>
-      <c r="BD1" s="140"/>
-      <c r="BE1" s="140"/>
-      <c r="BF1" s="140"/>
-      <c r="BG1" s="140"/>
-      <c r="BH1" s="140"/>
-      <c r="BI1" s="140"/>
-      <c r="BJ1" s="140"/>
-      <c r="BK1" s="140"/>
-      <c r="BL1" s="140"/>
-      <c r="BM1" s="140"/>
-      <c r="BN1" s="141"/>
+      <c r="AL1" s="199"/>
+      <c r="AM1" s="199"/>
+      <c r="AN1" s="199"/>
+      <c r="AO1" s="199"/>
+      <c r="AP1" s="199"/>
+      <c r="AQ1" s="199"/>
+      <c r="AR1" s="199"/>
+      <c r="AS1" s="199"/>
+      <c r="AT1" s="199"/>
+      <c r="AU1" s="199"/>
+      <c r="AV1" s="199"/>
+      <c r="AW1" s="199"/>
+      <c r="AX1" s="199"/>
+      <c r="AY1" s="199"/>
+      <c r="AZ1" s="199"/>
+      <c r="BA1" s="199"/>
+      <c r="BB1" s="199"/>
+      <c r="BC1" s="199"/>
+      <c r="BD1" s="199"/>
+      <c r="BE1" s="199"/>
+      <c r="BF1" s="199"/>
+      <c r="BG1" s="199"/>
+      <c r="BH1" s="199"/>
+      <c r="BI1" s="199"/>
+      <c r="BJ1" s="199"/>
+      <c r="BK1" s="199"/>
+      <c r="BL1" s="199"/>
+      <c r="BM1" s="199"/>
+      <c r="BN1" s="200"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="157"/>
+      <c r="A2" s="202"/>
+      <c r="B2" s="205"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="216"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3659,12 +3662,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="144"/>
-      <c r="B3" s="147"/>
-      <c r="C3" s="152"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="158"/>
+      <c r="A3" s="203"/>
+      <c r="B3" s="206"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="217"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -3847,20 +3850,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="159">
+      <c r="A4" s="193">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="162"/>
-      <c r="E4" s="165" t="s">
+      <c r="D4" s="195"/>
+      <c r="E4" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="167"/>
+      <c r="F4" s="196"/>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -3923,12 +3926,12 @@
       <c r="BN4" s="71"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="160"/>
+      <c r="A5" s="163"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="168"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="197"/>
       <c r="G5" s="122"/>
       <c r="H5" s="100"/>
       <c r="I5" s="123"/>
@@ -3991,18 +3994,18 @@
       <c r="BN5" s="119"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="169">
+      <c r="A6" s="149">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="177" t="s">
+      <c r="C6" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="178"/>
-      <c r="E6" s="181" t="s">
+      <c r="D6" s="158"/>
+      <c r="E6" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="182"/>
+      <c r="F6" s="189"/>
       <c r="G6" s="51"/>
       <c r="H6" s="62"/>
       <c r="I6" s="118"/>
@@ -4065,12 +4068,12 @@
       <c r="BN6" s="72"/>
     </row>
     <row r="7" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A7" s="160"/>
+      <c r="A7" s="163"/>
       <c r="B7" s="102"/>
-      <c r="C7" s="179"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="165"/>
-      <c r="F7" s="183"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="168"/>
+      <c r="F7" s="190"/>
       <c r="G7" s="101"/>
       <c r="H7" s="68"/>
       <c r="I7" s="96"/>
@@ -4133,20 +4136,20 @@
       <c r="BN7" s="72"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="169">
+      <c r="A8" s="149">
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="170" t="s">
+      <c r="C8" s="184" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="171"/>
-      <c r="E8" s="165" t="s">
+      <c r="D8" s="185"/>
+      <c r="E8" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="209"/>
+      <c r="F8" s="153"/>
       <c r="G8" s="50"/>
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
@@ -4209,12 +4212,12 @@
       <c r="BN8" s="95"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="160"/>
+      <c r="A9" s="163"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="172"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="186"/>
-      <c r="F9" s="200"/>
+      <c r="C9" s="186"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="154"/>
       <c r="G9" s="51"/>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
@@ -4277,18 +4280,18 @@
       <c r="BN9" s="72"/>
     </row>
     <row r="10" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A10" s="169">
+      <c r="A10" s="149">
         <v>4</v>
       </c>
       <c r="B10" s="36"/>
-      <c r="C10" s="170" t="s">
+      <c r="C10" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="171"/>
-      <c r="E10" s="187" t="s">
+      <c r="D10" s="185"/>
+      <c r="E10" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="199"/>
+      <c r="F10" s="155"/>
       <c r="G10" s="51"/>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
@@ -4351,12 +4354,12 @@
       <c r="BN10" s="95"/>
     </row>
     <row r="11" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A11" s="160"/>
+      <c r="A11" s="163"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="166"/>
-      <c r="F11" s="200"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="154"/>
       <c r="G11" s="51"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -4419,18 +4422,18 @@
       <c r="BN11" s="72"/>
     </row>
     <row r="12" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A12" s="169">
+      <c r="A12" s="149">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="170" t="s">
+      <c r="C12" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="171"/>
-      <c r="E12" s="190" t="s">
+      <c r="D12" s="185"/>
+      <c r="E12" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="199"/>
+      <c r="F12" s="155"/>
       <c r="G12" s="51"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63"/>
@@ -4493,12 +4496,12 @@
       <c r="BN12" s="95"/>
     </row>
     <row r="13" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A13" s="160"/>
+      <c r="A13" s="163"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="184"/>
-      <c r="D13" s="185"/>
-      <c r="E13" s="187"/>
-      <c r="F13" s="207"/>
+      <c r="C13" s="191"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="152"/>
+      <c r="F13" s="156"/>
       <c r="G13" s="53"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
@@ -4561,20 +4564,20 @@
       <c r="BN13" s="127"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="169">
+      <c r="A14" s="149">
         <v>6</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="170" t="s">
+      <c r="C14" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="171"/>
-      <c r="E14" s="166" t="s">
+      <c r="D14" s="185"/>
+      <c r="E14" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="175"/>
+      <c r="F14" s="183"/>
       <c r="G14" s="50"/>
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
@@ -4637,12 +4640,12 @@
       <c r="BN14" s="95"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="160"/>
+      <c r="A15" s="163"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="172"/>
-      <c r="D15" s="173"/>
-      <c r="E15" s="174"/>
-      <c r="F15" s="176"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="188"/>
+      <c r="F15" s="174"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -4705,18 +4708,18 @@
       <c r="BN15" s="126"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="169">
+      <c r="A16" s="149">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="177" t="s">
+      <c r="C16" s="157" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="178"/>
-      <c r="E16" s="190" t="s">
+      <c r="D16" s="158"/>
+      <c r="E16" s="151" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="191"/>
+      <c r="F16" s="173"/>
       <c r="G16" s="51"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -4779,12 +4782,12 @@
       <c r="BN16" s="95"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="160"/>
+      <c r="A17" s="163"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="188"/>
-      <c r="D17" s="189"/>
-      <c r="E17" s="187"/>
-      <c r="F17" s="175"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="183"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -4847,20 +4850,20 @@
       <c r="BN17" s="93"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="169">
+      <c r="A18" s="149">
         <v>8</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="192" t="s">
+      <c r="C18" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="193"/>
-      <c r="E18" s="165" t="s">
+      <c r="D18" s="144"/>
+      <c r="E18" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="194"/>
+      <c r="F18" s="178"/>
       <c r="G18" s="38"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
@@ -4923,12 +4926,12 @@
       <c r="BN18" s="133"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="160"/>
+      <c r="A19" s="163"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="163"/>
-      <c r="D19" s="164"/>
-      <c r="E19" s="166"/>
-      <c r="F19" s="176"/>
+      <c r="C19" s="159"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="174"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -4991,18 +4994,18 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="169">
+      <c r="A20" s="149">
         <v>9</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="177" t="s">
+      <c r="C20" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="178"/>
-      <c r="E20" s="181" t="s">
+      <c r="D20" s="158"/>
+      <c r="E20" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="191"/>
+      <c r="F20" s="173"/>
       <c r="G20" s="51"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -5065,12 +5068,12 @@
       <c r="BN20" s="95"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="160"/>
+      <c r="A21" s="163"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="163"/>
-      <c r="D21" s="164"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="176"/>
+      <c r="C21" s="159"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="172"/>
+      <c r="F21" s="174"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -5133,18 +5136,18 @@
       <c r="BN21" s="72"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="169">
+      <c r="A22" s="149">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="177" t="s">
+      <c r="C22" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="178"/>
-      <c r="E22" s="187" t="s">
+      <c r="D22" s="158"/>
+      <c r="E22" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="191"/>
+      <c r="F22" s="173"/>
       <c r="G22" s="52"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -5207,12 +5210,12 @@
       <c r="BN22" s="95"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="160"/>
+      <c r="A23" s="163"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="179"/>
-      <c r="D23" s="180"/>
-      <c r="E23" s="165"/>
-      <c r="F23" s="195"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="168"/>
+      <c r="F23" s="177"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5275,20 +5278,20 @@
       <c r="BN23" s="75"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="169">
+      <c r="A24" s="149">
         <v>11</v>
       </c>
-      <c r="B24" s="196" t="s">
+      <c r="B24" s="179" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="192" t="s">
+      <c r="C24" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="193"/>
-      <c r="E24" s="165" t="s">
+      <c r="D24" s="144"/>
+      <c r="E24" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="194"/>
+      <c r="F24" s="178"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5351,12 +5354,12 @@
       <c r="BN24" s="133"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="160"/>
-      <c r="B25" s="197"/>
-      <c r="C25" s="163"/>
-      <c r="D25" s="164"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="176"/>
+      <c r="A25" s="163"/>
+      <c r="B25" s="180"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="160"/>
+      <c r="E25" s="172"/>
+      <c r="F25" s="174"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5419,18 +5422,18 @@
       <c r="BN25" s="77"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="169">
+      <c r="A26" s="149">
         <v>12</v>
       </c>
-      <c r="B26" s="197"/>
-      <c r="C26" s="208" t="s">
+      <c r="B26" s="180"/>
+      <c r="C26" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="189"/>
-      <c r="E26" s="187" t="s">
+      <c r="D26" s="162"/>
+      <c r="E26" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="209"/>
+      <c r="F26" s="153"/>
       <c r="G26" s="50"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -5493,12 +5496,12 @@
       <c r="BN26" s="95"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="160"/>
-      <c r="B27" s="197"/>
-      <c r="C27" s="163"/>
-      <c r="D27" s="164"/>
-      <c r="E27" s="166"/>
-      <c r="F27" s="200"/>
+      <c r="A27" s="163"/>
+      <c r="B27" s="180"/>
+      <c r="C27" s="159"/>
+      <c r="D27" s="160"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="154"/>
       <c r="G27" s="51"/>
       <c r="H27" s="91"/>
       <c r="I27" s="7"/>
@@ -5561,18 +5564,18 @@
       <c r="BN27" s="77"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="169">
+      <c r="A28" s="149">
         <v>13</v>
       </c>
-      <c r="B28" s="197"/>
-      <c r="C28" s="177" t="s">
+      <c r="B28" s="180"/>
+      <c r="C28" s="157" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="178"/>
-      <c r="E28" s="181" t="s">
+      <c r="D28" s="158"/>
+      <c r="E28" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="199"/>
+      <c r="F28" s="155"/>
       <c r="G28" s="50"/>
       <c r="H28" s="9"/>
       <c r="I28" s="7"/>
@@ -5635,12 +5638,12 @@
       <c r="BN28" s="95"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="160"/>
-      <c r="B29" s="197"/>
-      <c r="C29" s="163"/>
-      <c r="D29" s="164"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="200"/>
+      <c r="A29" s="163"/>
+      <c r="B29" s="180"/>
+      <c r="C29" s="159"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="154"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="91"/>
@@ -5703,18 +5706,18 @@
       <c r="BN29" s="77"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="169">
+      <c r="A30" s="149">
         <v>14</v>
       </c>
-      <c r="B30" s="197"/>
-      <c r="C30" s="177" t="s">
+      <c r="B30" s="180"/>
+      <c r="C30" s="157" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="178"/>
-      <c r="E30" s="181" t="s">
+      <c r="D30" s="158"/>
+      <c r="E30" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F30" s="199"/>
+      <c r="F30" s="155"/>
       <c r="G30" s="50"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -5777,12 +5780,12 @@
       <c r="BN30" s="95"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="160"/>
-      <c r="B31" s="197"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="186"/>
-      <c r="F31" s="200"/>
+      <c r="A31" s="163"/>
+      <c r="B31" s="180"/>
+      <c r="C31" s="159"/>
+      <c r="D31" s="160"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="154"/>
       <c r="G31" s="51"/>
       <c r="H31" s="91"/>
       <c r="I31" s="7"/>
@@ -5845,18 +5848,18 @@
       <c r="BN31" s="77"/>
     </row>
     <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="169">
+      <c r="A32" s="149">
         <v>15</v>
       </c>
-      <c r="B32" s="197"/>
-      <c r="C32" s="177" t="s">
+      <c r="B32" s="180"/>
+      <c r="C32" s="157" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="178"/>
-      <c r="E32" s="187" t="s">
+      <c r="D32" s="158"/>
+      <c r="E32" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="199"/>
+      <c r="F32" s="155"/>
       <c r="G32" s="52"/>
       <c r="H32" s="24"/>
       <c r="I32" s="24"/>
@@ -5919,12 +5922,12 @@
       <c r="BN32" s="95"/>
     </row>
     <row r="33" spans="1:67" ht="12" customHeight="1">
-      <c r="A33" s="160"/>
-      <c r="B33" s="197"/>
-      <c r="C33" s="163"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="166"/>
-      <c r="F33" s="200"/>
+      <c r="A33" s="163"/>
+      <c r="B33" s="180"/>
+      <c r="C33" s="159"/>
+      <c r="D33" s="160"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="154"/>
       <c r="G33" s="52"/>
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
@@ -5987,18 +5990,18 @@
       <c r="BN33" s="77"/>
     </row>
     <row r="34" spans="1:67" ht="12" customHeight="1">
-      <c r="A34" s="169">
+      <c r="A34" s="149">
         <v>16</v>
       </c>
-      <c r="B34" s="197"/>
-      <c r="C34" s="177" t="s">
+      <c r="B34" s="180"/>
+      <c r="C34" s="157" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="178"/>
-      <c r="E34" s="181" t="s">
+      <c r="D34" s="158"/>
+      <c r="E34" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F34" s="199"/>
+      <c r="F34" s="155"/>
       <c r="G34" s="52"/>
       <c r="H34" s="24"/>
       <c r="I34" s="24"/>
@@ -6061,12 +6064,12 @@
       <c r="BN34" s="95"/>
     </row>
     <row r="35" spans="1:67" ht="12" customHeight="1">
-      <c r="A35" s="160"/>
-      <c r="B35" s="197"/>
-      <c r="C35" s="163"/>
-      <c r="D35" s="164"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="200"/>
+      <c r="A35" s="163"/>
+      <c r="B35" s="180"/>
+      <c r="C35" s="159"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="139"/>
+      <c r="F35" s="154"/>
       <c r="G35" s="52"/>
       <c r="H35" s="24"/>
       <c r="I35" s="24"/>
@@ -6129,18 +6132,18 @@
       <c r="BN35" s="77"/>
     </row>
     <row r="36" spans="1:67" ht="12" customHeight="1">
-      <c r="A36" s="169">
+      <c r="A36" s="149">
         <v>17</v>
       </c>
-      <c r="B36" s="197"/>
+      <c r="B36" s="180"/>
       <c r="C36" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D36" s="113"/>
-      <c r="E36" s="181" t="s">
+      <c r="E36" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="199"/>
+      <c r="F36" s="155"/>
       <c r="G36" s="52"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -6203,12 +6206,12 @@
       <c r="BN36" s="95"/>
     </row>
     <row r="37" spans="1:67" ht="12" customHeight="1">
-      <c r="A37" s="160"/>
-      <c r="B37" s="198"/>
+      <c r="A37" s="163"/>
+      <c r="B37" s="181"/>
       <c r="C37" s="114"/>
       <c r="D37" s="115"/>
-      <c r="E37" s="165"/>
-      <c r="F37" s="207"/>
+      <c r="E37" s="168"/>
+      <c r="F37" s="156"/>
       <c r="G37" s="54"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -6271,20 +6274,20 @@
       <c r="BN37" s="75"/>
     </row>
     <row r="38" spans="1:67" ht="12" customHeight="1">
-      <c r="A38" s="169">
+      <c r="A38" s="149">
         <v>20</v>
       </c>
       <c r="B38" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="201" t="s">
+      <c r="C38" s="164" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="202"/>
-      <c r="E38" s="165" t="s">
+      <c r="D38" s="165"/>
+      <c r="E38" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="205"/>
+      <c r="F38" s="169"/>
       <c r="G38" s="38"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -6348,12 +6351,12 @@
       <c r="BO38" s="97"/>
     </row>
     <row r="39" spans="1:67" ht="12" customHeight="1">
-      <c r="A39" s="160"/>
+      <c r="A39" s="163"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="203"/>
-      <c r="D39" s="204"/>
-      <c r="E39" s="165"/>
-      <c r="F39" s="206"/>
+      <c r="C39" s="166"/>
+      <c r="D39" s="167"/>
+      <c r="E39" s="168"/>
+      <c r="F39" s="170"/>
       <c r="G39" s="51"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -6403,9 +6406,9 @@
       <c r="BA39" s="63"/>
       <c r="BB39" s="13"/>
       <c r="BC39" s="19"/>
-      <c r="BD39" s="63"/>
-      <c r="BE39" s="63"/>
-      <c r="BF39" s="96"/>
+      <c r="BD39" s="129"/>
+      <c r="BE39" s="129"/>
+      <c r="BF39" s="129"/>
       <c r="BG39" s="96"/>
       <c r="BH39" s="96"/>
       <c r="BI39" s="13"/>
@@ -6417,20 +6420,20 @@
       <c r="BO39" s="97"/>
     </row>
     <row r="40" spans="1:67">
-      <c r="A40" s="169">
+      <c r="A40" s="149">
         <v>21</v>
       </c>
-      <c r="B40" s="211" t="s">
+      <c r="B40" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="192" t="s">
+      <c r="C40" s="143" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="193"/>
-      <c r="E40" s="166" t="s">
+      <c r="D40" s="144"/>
+      <c r="E40" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="F40" s="215"/>
+      <c r="F40" s="147"/>
       <c r="G40" s="38"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -6494,12 +6497,12 @@
       <c r="BO40" s="97"/>
     </row>
     <row r="41" spans="1:67" ht="10.199999999999999" thickBot="1">
-      <c r="A41" s="217"/>
-      <c r="B41" s="212"/>
-      <c r="C41" s="213"/>
-      <c r="D41" s="214"/>
-      <c r="E41" s="210"/>
-      <c r="F41" s="216"/>
+      <c r="A41" s="150"/>
+      <c r="B41" s="142"/>
+      <c r="C41" s="145"/>
+      <c r="D41" s="146"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="148"/>
       <c r="G41" s="39"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -6551,9 +6554,9 @@
       <c r="BC41" s="20"/>
       <c r="BD41" s="69"/>
       <c r="BE41" s="69"/>
-      <c r="BF41" s="69"/>
-      <c r="BG41" s="69"/>
-      <c r="BH41" s="69"/>
+      <c r="BF41" s="245"/>
+      <c r="BG41" s="245"/>
+      <c r="BH41" s="245"/>
       <c r="BI41" s="14"/>
       <c r="BJ41" s="20"/>
       <c r="BK41" s="69"/>
@@ -6584,23 +6587,57 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B24:B37"/>
+    <mergeCell ref="F34:F35"/>
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="C38:D39"/>
     <mergeCell ref="E38:E39"/>
@@ -6617,57 +6654,23 @@
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="E28:E29"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B24:B37"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="A40:A41"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -6703,54 +6706,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="145" t="s">
+      <c r="B1" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="149"/>
-      <c r="E1" s="154" t="s">
+      <c r="D1" s="208"/>
+      <c r="E1" s="213" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="156" t="s">
+      <c r="F1" s="215" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="139"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="140"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="140"/>
-      <c r="AD1" s="141"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="199"/>
+      <c r="K1" s="199"/>
+      <c r="L1" s="199"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="199"/>
+      <c r="O1" s="199"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="199"/>
+      <c r="Y1" s="199"/>
+      <c r="Z1" s="199"/>
+      <c r="AA1" s="199"/>
+      <c r="AB1" s="199"/>
+      <c r="AC1" s="199"/>
+      <c r="AD1" s="200"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="143"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="157"/>
+      <c r="A2" s="202"/>
+      <c r="B2" s="205"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="216"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -6825,12 +6828,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="144"/>
-      <c r="B3" s="147"/>
-      <c r="C3" s="152"/>
-      <c r="D3" s="153"/>
-      <c r="E3" s="244"/>
-      <c r="F3" s="158"/>
+      <c r="A3" s="203"/>
+      <c r="B3" s="206"/>
+      <c r="C3" s="211"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="218"/>
+      <c r="F3" s="217"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -6905,20 +6908,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="159">
+      <c r="A4" s="193">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="162"/>
-      <c r="E4" s="237" t="s">
+      <c r="D4" s="195"/>
+      <c r="E4" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="167"/>
+      <c r="F4" s="196"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -6941,20 +6944,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="238" t="s">
+      <c r="AC4" s="225" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="232" t="s">
+      <c r="AD4" s="219" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="160"/>
+      <c r="A5" s="163"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="168"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="197"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -6977,22 +6980,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="239"/>
-      <c r="AD5" s="233"/>
+      <c r="AC5" s="226"/>
+      <c r="AD5" s="220"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="169">
+      <c r="A6" s="149">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="177" t="s">
+      <c r="C6" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="178"/>
-      <c r="E6" s="235" t="s">
+      <c r="D6" s="158"/>
+      <c r="E6" s="222" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="182"/>
+      <c r="F6" s="189"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -7015,16 +7018,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="239"/>
-      <c r="AD6" s="233"/>
+      <c r="AC6" s="226"/>
+      <c r="AD6" s="220"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="160"/>
+      <c r="A7" s="163"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="179"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="183"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="190"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -7047,24 +7050,24 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="239"/>
-      <c r="AD7" s="233"/>
+      <c r="AC7" s="226"/>
+      <c r="AD7" s="220"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="221">
+      <c r="A8" s="228">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="241" t="s">
+      <c r="C8" s="230" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="242"/>
-      <c r="E8" s="243" t="s">
+      <c r="D8" s="231"/>
+      <c r="E8" s="232" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="194"/>
+      <c r="F8" s="178"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -7087,16 +7090,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="239"/>
-      <c r="AD8" s="233"/>
+      <c r="AC8" s="226"/>
+      <c r="AD8" s="220"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="222"/>
+      <c r="A9" s="229"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="227"/>
-      <c r="F9" s="195"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="192"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="177"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -7119,24 +7122,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="239"/>
-      <c r="AD9" s="233"/>
+      <c r="AC9" s="226"/>
+      <c r="AD9" s="220"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="230">
+      <c r="A10" s="234">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="170" t="s">
+      <c r="C10" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="171"/>
-      <c r="E10" s="229" t="s">
+      <c r="D10" s="185"/>
+      <c r="E10" s="235" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="175"/>
+      <c r="F10" s="183"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -7159,16 +7162,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="239"/>
-      <c r="AD10" s="233"/>
+      <c r="AC10" s="226"/>
+      <c r="AD10" s="220"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="222"/>
+      <c r="A11" s="229"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="225"/>
-      <c r="F11" s="176"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="236"/>
+      <c r="F11" s="174"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -7191,22 +7194,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="239"/>
-      <c r="AD11" s="233"/>
+      <c r="AC11" s="226"/>
+      <c r="AD11" s="220"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="221">
+      <c r="A12" s="228">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="177" t="s">
+      <c r="C12" s="157" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="178"/>
-      <c r="E12" s="231" t="s">
+      <c r="D12" s="158"/>
+      <c r="E12" s="237" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="191"/>
+      <c r="F12" s="173"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7229,16 +7232,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="239"/>
-      <c r="AD12" s="233"/>
+      <c r="AC12" s="226"/>
+      <c r="AD12" s="220"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="230"/>
+      <c r="A13" s="234"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="188"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="229"/>
-      <c r="F13" s="175"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="162"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="183"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7261,24 +7264,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="239"/>
-      <c r="AD13" s="233"/>
+      <c r="AC13" s="226"/>
+      <c r="AD13" s="220"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="226">
+      <c r="A14" s="238">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="192" t="s">
+      <c r="C14" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="193"/>
-      <c r="E14" s="228" t="s">
+      <c r="D14" s="144"/>
+      <c r="E14" s="239" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="194"/>
+      <c r="F14" s="178"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7301,16 +7304,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="239"/>
-      <c r="AD14" s="233"/>
+      <c r="AC14" s="226"/>
+      <c r="AD14" s="220"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="226"/>
+      <c r="A15" s="238"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="163"/>
-      <c r="D15" s="164"/>
-      <c r="E15" s="225"/>
-      <c r="F15" s="176"/>
+      <c r="C15" s="159"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="236"/>
+      <c r="F15" s="174"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7333,22 +7336,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="239"/>
-      <c r="AD15" s="233"/>
+      <c r="AC15" s="226"/>
+      <c r="AD15" s="220"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="226">
+      <c r="A16" s="238">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="177" t="s">
+      <c r="C16" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="178"/>
-      <c r="E16" s="224" t="s">
+      <c r="D16" s="158"/>
+      <c r="E16" s="240" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="191"/>
+      <c r="F16" s="173"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7371,16 +7374,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="239"/>
-      <c r="AD16" s="233"/>
+      <c r="AC16" s="226"/>
+      <c r="AD16" s="220"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="226"/>
+      <c r="A17" s="238"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="163"/>
-      <c r="D17" s="164"/>
-      <c r="E17" s="225"/>
-      <c r="F17" s="176"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="160"/>
+      <c r="E17" s="236"/>
+      <c r="F17" s="174"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7403,22 +7406,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="239"/>
-      <c r="AD17" s="233"/>
+      <c r="AC17" s="226"/>
+      <c r="AD17" s="220"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="226">
+      <c r="A18" s="238">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="177" t="s">
+      <c r="C18" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="178"/>
-      <c r="E18" s="224" t="s">
+      <c r="D18" s="158"/>
+      <c r="E18" s="240" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="191"/>
+      <c r="F18" s="173"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7441,16 +7444,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="239"/>
-      <c r="AD18" s="233"/>
+      <c r="AC18" s="226"/>
+      <c r="AD18" s="220"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="226"/>
+      <c r="A19" s="238"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="179"/>
-      <c r="D19" s="180"/>
-      <c r="E19" s="227"/>
-      <c r="F19" s="195"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="233"/>
+      <c r="F19" s="177"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7473,24 +7476,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="239"/>
-      <c r="AD19" s="233"/>
+      <c r="AC19" s="226"/>
+      <c r="AD19" s="220"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="221">
+      <c r="A20" s="228">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="192" t="s">
+      <c r="C20" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="193"/>
-      <c r="E20" s="228" t="s">
+      <c r="D20" s="144"/>
+      <c r="E20" s="239" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="194"/>
+      <c r="F20" s="178"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -7513,18 +7516,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="239"/>
-      <c r="AD20" s="233"/>
+      <c r="AC20" s="226"/>
+      <c r="AD20" s="220"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="222"/>
+      <c r="A21" s="229"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="163"/>
-      <c r="D21" s="164"/>
-      <c r="E21" s="225"/>
-      <c r="F21" s="176"/>
+      <c r="C21" s="159"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="236"/>
+      <c r="F21" s="174"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -7547,22 +7550,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="239"/>
-      <c r="AD21" s="233"/>
+      <c r="AC21" s="226"/>
+      <c r="AD21" s="220"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="221">
+      <c r="A22" s="228">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="223" t="s">
+      <c r="C22" s="241" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="178"/>
-      <c r="E22" s="224" t="s">
+      <c r="D22" s="158"/>
+      <c r="E22" s="240" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="191"/>
+      <c r="F22" s="173"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -7585,16 +7588,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="239"/>
-      <c r="AD22" s="233"/>
+      <c r="AC22" s="226"/>
+      <c r="AD22" s="220"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="222"/>
+      <c r="A23" s="229"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="163"/>
-      <c r="D23" s="164"/>
-      <c r="E23" s="225"/>
-      <c r="F23" s="176"/>
+      <c r="C23" s="159"/>
+      <c r="D23" s="160"/>
+      <c r="E23" s="236"/>
+      <c r="F23" s="174"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -7617,22 +7620,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="239"/>
-      <c r="AD23" s="233"/>
+      <c r="AC23" s="226"/>
+      <c r="AD23" s="220"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="221">
+      <c r="A24" s="228">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="223" t="s">
+      <c r="C24" s="241" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="178"/>
-      <c r="E24" s="224" t="s">
+      <c r="D24" s="158"/>
+      <c r="E24" s="240" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="191"/>
+      <c r="F24" s="173"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -7655,16 +7658,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="239"/>
-      <c r="AD24" s="233"/>
+      <c r="AC24" s="226"/>
+      <c r="AD24" s="220"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="222"/>
+      <c r="A25" s="229"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="163"/>
-      <c r="D25" s="164"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="195"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="160"/>
+      <c r="E25" s="236"/>
+      <c r="F25" s="177"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7687,24 +7690,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="239"/>
-      <c r="AD25" s="233"/>
+      <c r="AC25" s="226"/>
+      <c r="AD25" s="220"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="169">
+      <c r="A26" s="149">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="201" t="s">
+      <c r="C26" s="164" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="202"/>
-      <c r="E26" s="218" t="s">
+      <c r="D26" s="165"/>
+      <c r="E26" s="242" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="205"/>
+      <c r="F26" s="169"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -7727,16 +7730,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="239"/>
-      <c r="AD26" s="233"/>
+      <c r="AC26" s="226"/>
+      <c r="AD26" s="220"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="160"/>
+      <c r="A27" s="163"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="203"/>
-      <c r="D27" s="204"/>
-      <c r="E27" s="219"/>
-      <c r="F27" s="206"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="167"/>
+      <c r="E27" s="243"/>
+      <c r="F27" s="170"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -7759,24 +7762,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="239"/>
-      <c r="AD27" s="233"/>
+      <c r="AC27" s="226"/>
+      <c r="AD27" s="220"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="169">
+      <c r="A28" s="149">
         <v>14</v>
       </c>
-      <c r="B28" s="211" t="s">
+      <c r="B28" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="192" t="s">
+      <c r="C28" s="143" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="193"/>
-      <c r="E28" s="211" t="s">
+      <c r="D28" s="144"/>
+      <c r="E28" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="215"/>
+      <c r="F28" s="147"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -7799,16 +7802,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="239"/>
-      <c r="AD28" s="233"/>
+      <c r="AC28" s="226"/>
+      <c r="AD28" s="220"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="220"/>
-      <c r="B29" s="212"/>
-      <c r="C29" s="213"/>
-      <c r="D29" s="214"/>
-      <c r="E29" s="212"/>
-      <c r="F29" s="216"/>
+      <c r="A29" s="244"/>
+      <c r="B29" s="142"/>
+      <c r="C29" s="145"/>
+      <c r="D29" s="146"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="148"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -7831,8 +7834,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="240"/>
-      <c r="AD29" s="234"/>
+      <c r="AC29" s="227"/>
+      <c r="AD29" s="221"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -7852,12 +7855,45 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -7874,45 +7910,12 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/099-納品物/000-要件定義/003-WBS-納品版.xlsx
+++ b/099-納品物/000-要件定義/003-WBS-納品版.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\099-納品物\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6636C90D-2BE2-4AE9-9C4D-C0FBAECBABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD50C1D-3515-4AE4-BC6C-6D8C3107A3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2139,9 +2139,222 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2151,12 +2364,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2169,296 +2376,89 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="81" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3333,94 +3333,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="204" t="s">
+      <c r="B1" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="207" t="s">
+      <c r="C1" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="208"/>
-      <c r="E1" s="213" t="s">
+      <c r="D1" s="150"/>
+      <c r="E1" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="215" t="s">
+      <c r="F1" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="198">
+      <c r="G1" s="140">
         <v>45536</v>
       </c>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="199"/>
-      <c r="O1" s="199"/>
-      <c r="P1" s="199"/>
-      <c r="Q1" s="199"/>
-      <c r="R1" s="199"/>
-      <c r="S1" s="199"/>
-      <c r="T1" s="199"/>
-      <c r="U1" s="199"/>
-      <c r="V1" s="199"/>
-      <c r="W1" s="199"/>
-      <c r="X1" s="199"/>
-      <c r="Y1" s="199"/>
-      <c r="Z1" s="199"/>
-      <c r="AA1" s="199"/>
-      <c r="AB1" s="199"/>
-      <c r="AC1" s="199"/>
-      <c r="AD1" s="199"/>
-      <c r="AE1" s="199"/>
-      <c r="AF1" s="199"/>
-      <c r="AG1" s="199"/>
-      <c r="AH1" s="199"/>
-      <c r="AI1" s="199"/>
-      <c r="AJ1" s="200"/>
-      <c r="AK1" s="198">
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="141"/>
+      <c r="AE1" s="141"/>
+      <c r="AF1" s="141"/>
+      <c r="AG1" s="141"/>
+      <c r="AH1" s="141"/>
+      <c r="AI1" s="141"/>
+      <c r="AJ1" s="142"/>
+      <c r="AK1" s="140">
         <v>45566</v>
       </c>
-      <c r="AL1" s="199"/>
-      <c r="AM1" s="199"/>
-      <c r="AN1" s="199"/>
-      <c r="AO1" s="199"/>
-      <c r="AP1" s="199"/>
-      <c r="AQ1" s="199"/>
-      <c r="AR1" s="199"/>
-      <c r="AS1" s="199"/>
-      <c r="AT1" s="199"/>
-      <c r="AU1" s="199"/>
-      <c r="AV1" s="199"/>
-      <c r="AW1" s="199"/>
-      <c r="AX1" s="199"/>
-      <c r="AY1" s="199"/>
-      <c r="AZ1" s="199"/>
-      <c r="BA1" s="199"/>
-      <c r="BB1" s="199"/>
-      <c r="BC1" s="199"/>
-      <c r="BD1" s="199"/>
-      <c r="BE1" s="199"/>
-      <c r="BF1" s="199"/>
-      <c r="BG1" s="199"/>
-      <c r="BH1" s="199"/>
-      <c r="BI1" s="199"/>
-      <c r="BJ1" s="199"/>
-      <c r="BK1" s="199"/>
-      <c r="BL1" s="199"/>
-      <c r="BM1" s="199"/>
-      <c r="BN1" s="200"/>
+      <c r="AL1" s="141"/>
+      <c r="AM1" s="141"/>
+      <c r="AN1" s="141"/>
+      <c r="AO1" s="141"/>
+      <c r="AP1" s="141"/>
+      <c r="AQ1" s="141"/>
+      <c r="AR1" s="141"/>
+      <c r="AS1" s="141"/>
+      <c r="AT1" s="141"/>
+      <c r="AU1" s="141"/>
+      <c r="AV1" s="141"/>
+      <c r="AW1" s="141"/>
+      <c r="AX1" s="141"/>
+      <c r="AY1" s="141"/>
+      <c r="AZ1" s="141"/>
+      <c r="BA1" s="141"/>
+      <c r="BB1" s="141"/>
+      <c r="BC1" s="141"/>
+      <c r="BD1" s="141"/>
+      <c r="BE1" s="141"/>
+      <c r="BF1" s="141"/>
+      <c r="BG1" s="141"/>
+      <c r="BH1" s="141"/>
+      <c r="BI1" s="141"/>
+      <c r="BJ1" s="141"/>
+      <c r="BK1" s="141"/>
+      <c r="BL1" s="141"/>
+      <c r="BM1" s="141"/>
+      <c r="BN1" s="142"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="202"/>
-      <c r="B2" s="205"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="216"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="158"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3662,12 +3662,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="203"/>
-      <c r="B3" s="206"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="214"/>
-      <c r="F3" s="217"/>
+      <c r="A3" s="145"/>
+      <c r="B3" s="148"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="159"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -3850,20 +3850,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="193">
+      <c r="A4" s="160">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="195"/>
-      <c r="E4" s="168" t="s">
+      <c r="D4" s="163"/>
+      <c r="E4" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="196"/>
+      <c r="F4" s="168"/>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -3926,12 +3926,12 @@
       <c r="BN4" s="71"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="163"/>
+      <c r="A5" s="161"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="197"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="165"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="169"/>
       <c r="G5" s="122"/>
       <c r="H5" s="100"/>
       <c r="I5" s="123"/>
@@ -3994,18 +3994,18 @@
       <c r="BN5" s="119"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="149">
+      <c r="A6" s="170">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="157" t="s">
+      <c r="C6" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="158"/>
-      <c r="E6" s="171" t="s">
+      <c r="D6" s="179"/>
+      <c r="E6" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="189"/>
+      <c r="F6" s="183"/>
       <c r="G6" s="51"/>
       <c r="H6" s="62"/>
       <c r="I6" s="118"/>
@@ -4068,12 +4068,12 @@
       <c r="BN6" s="72"/>
     </row>
     <row r="7" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A7" s="163"/>
+      <c r="A7" s="161"/>
       <c r="B7" s="102"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="168"/>
-      <c r="F7" s="190"/>
+      <c r="C7" s="180"/>
+      <c r="D7" s="181"/>
+      <c r="E7" s="166"/>
+      <c r="F7" s="184"/>
       <c r="G7" s="101"/>
       <c r="H7" s="68"/>
       <c r="I7" s="96"/>
@@ -4136,20 +4136,20 @@
       <c r="BN7" s="72"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="149">
+      <c r="A8" s="170">
         <v>3</v>
       </c>
       <c r="B8" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="184" t="s">
+      <c r="C8" s="171" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="185"/>
-      <c r="E8" s="168" t="s">
+      <c r="D8" s="172"/>
+      <c r="E8" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="153"/>
+      <c r="F8" s="210"/>
       <c r="G8" s="50"/>
       <c r="H8" s="62"/>
       <c r="I8" s="62"/>
@@ -4212,12 +4212,12 @@
       <c r="BN8" s="95"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="163"/>
+      <c r="A9" s="161"/>
       <c r="B9" s="36"/>
-      <c r="C9" s="186"/>
-      <c r="D9" s="187"/>
-      <c r="E9" s="172"/>
-      <c r="F9" s="154"/>
+      <c r="C9" s="173"/>
+      <c r="D9" s="174"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="201"/>
       <c r="G9" s="51"/>
       <c r="H9" s="63"/>
       <c r="I9" s="63"/>
@@ -4280,18 +4280,18 @@
       <c r="BN9" s="72"/>
     </row>
     <row r="10" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A10" s="149">
+      <c r="A10" s="170">
         <v>4</v>
       </c>
       <c r="B10" s="36"/>
-      <c r="C10" s="184" t="s">
+      <c r="C10" s="171" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="185"/>
-      <c r="E10" s="152" t="s">
+      <c r="D10" s="172"/>
+      <c r="E10" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="155"/>
+      <c r="F10" s="200"/>
       <c r="G10" s="51"/>
       <c r="H10" s="63"/>
       <c r="I10" s="63"/>
@@ -4354,12 +4354,12 @@
       <c r="BN10" s="95"/>
     </row>
     <row r="11" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A11" s="163"/>
+      <c r="A11" s="161"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="139"/>
-      <c r="F11" s="154"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="174"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="201"/>
       <c r="G11" s="51"/>
       <c r="H11" s="63"/>
       <c r="I11" s="63"/>
@@ -4422,18 +4422,18 @@
       <c r="BN11" s="72"/>
     </row>
     <row r="12" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A12" s="149">
+      <c r="A12" s="170">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="184" t="s">
+      <c r="C12" s="171" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="185"/>
-      <c r="E12" s="151" t="s">
+      <c r="D12" s="172"/>
+      <c r="E12" s="191" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="155"/>
+      <c r="F12" s="200"/>
       <c r="G12" s="51"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63"/>
@@ -4496,12 +4496,12 @@
       <c r="BN12" s="95"/>
     </row>
     <row r="13" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A13" s="163"/>
+      <c r="A13" s="161"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="191"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="156"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="186"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="208"/>
       <c r="G13" s="53"/>
       <c r="H13" s="66"/>
       <c r="I13" s="66"/>
@@ -4564,20 +4564,20 @@
       <c r="BN13" s="127"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="149">
+      <c r="A14" s="170">
         <v>6</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="184" t="s">
+      <c r="C14" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="185"/>
-      <c r="E14" s="139" t="s">
+      <c r="D14" s="172"/>
+      <c r="E14" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="183"/>
+      <c r="F14" s="176"/>
       <c r="G14" s="50"/>
       <c r="H14" s="62"/>
       <c r="I14" s="62"/>
@@ -4640,12 +4640,12 @@
       <c r="BN14" s="95"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="163"/>
+      <c r="A15" s="161"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="187"/>
-      <c r="E15" s="188"/>
-      <c r="F15" s="174"/>
+      <c r="C15" s="173"/>
+      <c r="D15" s="174"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="177"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -4708,18 +4708,18 @@
       <c r="BN15" s="126"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="149">
+      <c r="A16" s="170">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="157" t="s">
+      <c r="C16" s="178" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="158"/>
-      <c r="E16" s="151" t="s">
+      <c r="D16" s="179"/>
+      <c r="E16" s="191" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="173"/>
+      <c r="F16" s="192"/>
       <c r="G16" s="51"/>
       <c r="H16" s="63"/>
       <c r="I16" s="63"/>
@@ -4782,12 +4782,12 @@
       <c r="BN16" s="95"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="163"/>
+      <c r="A17" s="161"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="162"/>
-      <c r="E17" s="152"/>
-      <c r="F17" s="183"/>
+      <c r="C17" s="189"/>
+      <c r="D17" s="190"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="176"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -4850,20 +4850,20 @@
       <c r="BN17" s="93"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="149">
+      <c r="A18" s="170">
         <v>8</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="143" t="s">
+      <c r="C18" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="144"/>
-      <c r="E18" s="168" t="s">
+      <c r="D18" s="194"/>
+      <c r="E18" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="178"/>
+      <c r="F18" s="195"/>
       <c r="G18" s="38"/>
       <c r="H18" s="65"/>
       <c r="I18" s="65"/>
@@ -4926,12 +4926,12 @@
       <c r="BN18" s="133"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="163"/>
+      <c r="A19" s="161"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="159"/>
-      <c r="D19" s="160"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="174"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="177"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -4994,18 +4994,18 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="149">
+      <c r="A20" s="170">
         <v>9</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="157" t="s">
+      <c r="C20" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="158"/>
-      <c r="E20" s="171" t="s">
+      <c r="D20" s="179"/>
+      <c r="E20" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="173"/>
+      <c r="F20" s="192"/>
       <c r="G20" s="51"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -5068,12 +5068,12 @@
       <c r="BN20" s="95"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="163"/>
+      <c r="A21" s="161"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="159"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="174"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="187"/>
+      <c r="F21" s="177"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -5136,18 +5136,18 @@
       <c r="BN21" s="72"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="149">
+      <c r="A22" s="170">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="157" t="s">
+      <c r="C22" s="178" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="158"/>
-      <c r="E22" s="152" t="s">
+      <c r="D22" s="179"/>
+      <c r="E22" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="173"/>
+      <c r="F22" s="192"/>
       <c r="G22" s="52"/>
       <c r="H22" s="24"/>
       <c r="I22" s="24"/>
@@ -5210,12 +5210,12 @@
       <c r="BN22" s="95"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="163"/>
+      <c r="A23" s="161"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="176"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="177"/>
+      <c r="C23" s="180"/>
+      <c r="D23" s="181"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="196"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5278,20 +5278,20 @@
       <c r="BN23" s="75"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="149">
+      <c r="A24" s="170">
         <v>11</v>
       </c>
-      <c r="B24" s="179" t="s">
+      <c r="B24" s="197" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="143" t="s">
+      <c r="C24" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="144"/>
-      <c r="E24" s="168" t="s">
+      <c r="D24" s="194"/>
+      <c r="E24" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="178"/>
+      <c r="F24" s="195"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5354,12 +5354,12 @@
       <c r="BN24" s="133"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="163"/>
-      <c r="B25" s="180"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="172"/>
-      <c r="F25" s="174"/>
+      <c r="A25" s="161"/>
+      <c r="B25" s="198"/>
+      <c r="C25" s="164"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="187"/>
+      <c r="F25" s="177"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5422,18 +5422,18 @@
       <c r="BN25" s="77"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="149">
+      <c r="A26" s="170">
         <v>12</v>
       </c>
-      <c r="B26" s="180"/>
-      <c r="C26" s="161" t="s">
+      <c r="B26" s="198"/>
+      <c r="C26" s="209" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="162"/>
-      <c r="E26" s="152" t="s">
+      <c r="D26" s="190"/>
+      <c r="E26" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="153"/>
+      <c r="F26" s="210"/>
       <c r="G26" s="50"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
@@ -5496,12 +5496,12 @@
       <c r="BN26" s="95"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="163"/>
-      <c r="B27" s="180"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="160"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="154"/>
+      <c r="A27" s="161"/>
+      <c r="B27" s="198"/>
+      <c r="C27" s="164"/>
+      <c r="D27" s="165"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="201"/>
       <c r="G27" s="51"/>
       <c r="H27" s="91"/>
       <c r="I27" s="7"/>
@@ -5564,18 +5564,18 @@
       <c r="BN27" s="77"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="149">
+      <c r="A28" s="170">
         <v>13</v>
       </c>
-      <c r="B28" s="180"/>
-      <c r="C28" s="157" t="s">
+      <c r="B28" s="198"/>
+      <c r="C28" s="178" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="158"/>
-      <c r="E28" s="171" t="s">
+      <c r="D28" s="179"/>
+      <c r="E28" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="155"/>
+      <c r="F28" s="200"/>
       <c r="G28" s="50"/>
       <c r="H28" s="9"/>
       <c r="I28" s="7"/>
@@ -5638,12 +5638,12 @@
       <c r="BN28" s="95"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="163"/>
-      <c r="B29" s="180"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="160"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="154"/>
+      <c r="A29" s="161"/>
+      <c r="B29" s="198"/>
+      <c r="C29" s="164"/>
+      <c r="D29" s="165"/>
+      <c r="E29" s="167"/>
+      <c r="F29" s="201"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="91"/>
@@ -5706,18 +5706,18 @@
       <c r="BN29" s="77"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="149">
+      <c r="A30" s="170">
         <v>14</v>
       </c>
-      <c r="B30" s="180"/>
-      <c r="C30" s="157" t="s">
+      <c r="B30" s="198"/>
+      <c r="C30" s="178" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="158"/>
-      <c r="E30" s="171" t="s">
+      <c r="D30" s="179"/>
+      <c r="E30" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="F30" s="155"/>
+      <c r="F30" s="200"/>
       <c r="G30" s="50"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -5780,12 +5780,12 @@
       <c r="BN30" s="95"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="163"/>
-      <c r="B31" s="180"/>
-      <c r="C31" s="159"/>
-      <c r="D31" s="160"/>
-      <c r="E31" s="172"/>
-      <c r="F31" s="154"/>
+      <c r="A31" s="161"/>
+      <c r="B31" s="198"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="187"/>
+      <c r="F31" s="201"/>
       <c r="G31" s="51"/>
       <c r="H31" s="91"/>
       <c r="I31" s="7"/>
@@ -5848,18 +5848,18 @@
       <c r="BN31" s="77"/>
     </row>
     <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="149">
+      <c r="A32" s="170">
         <v>15</v>
       </c>
-      <c r="B32" s="180"/>
-      <c r="C32" s="157" t="s">
+      <c r="B32" s="198"/>
+      <c r="C32" s="178" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="158"/>
-      <c r="E32" s="152" t="s">
+      <c r="D32" s="179"/>
+      <c r="E32" s="188" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="155"/>
+      <c r="F32" s="200"/>
       <c r="G32" s="52"/>
       <c r="H32" s="24"/>
       <c r="I32" s="24"/>
@@ -5922,12 +5922,12 @@
       <c r="BN32" s="95"/>
     </row>
     <row r="33" spans="1:67" ht="12" customHeight="1">
-      <c r="A33" s="163"/>
-      <c r="B33" s="180"/>
-      <c r="C33" s="159"/>
-      <c r="D33" s="160"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="154"/>
+      <c r="A33" s="161"/>
+      <c r="B33" s="198"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="167"/>
+      <c r="F33" s="201"/>
       <c r="G33" s="52"/>
       <c r="H33" s="24"/>
       <c r="I33" s="24"/>
@@ -5990,18 +5990,18 @@
       <c r="BN33" s="77"/>
     </row>
     <row r="34" spans="1:67" ht="12" customHeight="1">
-      <c r="A34" s="149">
+      <c r="A34" s="170">
         <v>16</v>
       </c>
-      <c r="B34" s="180"/>
-      <c r="C34" s="157" t="s">
+      <c r="B34" s="198"/>
+      <c r="C34" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="158"/>
-      <c r="E34" s="171" t="s">
+      <c r="D34" s="179"/>
+      <c r="E34" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="F34" s="155"/>
+      <c r="F34" s="200"/>
       <c r="G34" s="52"/>
       <c r="H34" s="24"/>
       <c r="I34" s="24"/>
@@ -6064,12 +6064,12 @@
       <c r="BN34" s="95"/>
     </row>
     <row r="35" spans="1:67" ht="12" customHeight="1">
-      <c r="A35" s="163"/>
-      <c r="B35" s="180"/>
-      <c r="C35" s="159"/>
-      <c r="D35" s="160"/>
-      <c r="E35" s="139"/>
-      <c r="F35" s="154"/>
+      <c r="A35" s="161"/>
+      <c r="B35" s="198"/>
+      <c r="C35" s="164"/>
+      <c r="D35" s="165"/>
+      <c r="E35" s="167"/>
+      <c r="F35" s="201"/>
       <c r="G35" s="52"/>
       <c r="H35" s="24"/>
       <c r="I35" s="24"/>
@@ -6132,18 +6132,18 @@
       <c r="BN35" s="77"/>
     </row>
     <row r="36" spans="1:67" ht="12" customHeight="1">
-      <c r="A36" s="149">
+      <c r="A36" s="170">
         <v>17</v>
       </c>
-      <c r="B36" s="180"/>
+      <c r="B36" s="198"/>
       <c r="C36" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D36" s="113"/>
-      <c r="E36" s="171" t="s">
+      <c r="E36" s="182" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="155"/>
+      <c r="F36" s="200"/>
       <c r="G36" s="52"/>
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
@@ -6206,12 +6206,12 @@
       <c r="BN36" s="95"/>
     </row>
     <row r="37" spans="1:67" ht="12" customHeight="1">
-      <c r="A37" s="163"/>
-      <c r="B37" s="181"/>
+      <c r="A37" s="161"/>
+      <c r="B37" s="199"/>
       <c r="C37" s="114"/>
       <c r="D37" s="115"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="156"/>
+      <c r="E37" s="166"/>
+      <c r="F37" s="208"/>
       <c r="G37" s="54"/>
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
@@ -6274,20 +6274,20 @@
       <c r="BN37" s="75"/>
     </row>
     <row r="38" spans="1:67" ht="12" customHeight="1">
-      <c r="A38" s="149">
+      <c r="A38" s="170">
         <v>20</v>
       </c>
       <c r="B38" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="164" t="s">
+      <c r="C38" s="202" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="165"/>
-      <c r="E38" s="168" t="s">
+      <c r="D38" s="203"/>
+      <c r="E38" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="169"/>
+      <c r="F38" s="206"/>
       <c r="G38" s="38"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -6351,12 +6351,12 @@
       <c r="BO38" s="97"/>
     </row>
     <row r="39" spans="1:67" ht="12" customHeight="1">
-      <c r="A39" s="163"/>
+      <c r="A39" s="161"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="166"/>
-      <c r="D39" s="167"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="170"/>
+      <c r="C39" s="204"/>
+      <c r="D39" s="205"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="207"/>
       <c r="G39" s="51"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
@@ -6408,7 +6408,7 @@
       <c r="BC39" s="19"/>
       <c r="BD39" s="129"/>
       <c r="BE39" s="129"/>
-      <c r="BF39" s="129"/>
+      <c r="BF39" s="32"/>
       <c r="BG39" s="96"/>
       <c r="BH39" s="96"/>
       <c r="BI39" s="13"/>
@@ -6420,20 +6420,20 @@
       <c r="BO39" s="97"/>
     </row>
     <row r="40" spans="1:67">
-      <c r="A40" s="149">
+      <c r="A40" s="170">
         <v>21</v>
       </c>
-      <c r="B40" s="141" t="s">
+      <c r="B40" s="212" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="143" t="s">
+      <c r="C40" s="193" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="144"/>
-      <c r="E40" s="139" t="s">
+      <c r="D40" s="194"/>
+      <c r="E40" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="F40" s="147"/>
+      <c r="F40" s="216"/>
       <c r="G40" s="38"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
@@ -6485,7 +6485,7 @@
       <c r="BC40" s="21"/>
       <c r="BD40" s="65"/>
       <c r="BE40" s="65"/>
-      <c r="BF40" s="30"/>
+      <c r="BF40" s="60"/>
       <c r="BG40" s="30"/>
       <c r="BH40" s="30"/>
       <c r="BI40" s="15"/>
@@ -6497,12 +6497,12 @@
       <c r="BO40" s="97"/>
     </row>
     <row r="41" spans="1:67" ht="10.199999999999999" thickBot="1">
-      <c r="A41" s="150"/>
-      <c r="B41" s="142"/>
-      <c r="C41" s="145"/>
-      <c r="D41" s="146"/>
-      <c r="E41" s="140"/>
-      <c r="F41" s="148"/>
+      <c r="A41" s="218"/>
+      <c r="B41" s="213"/>
+      <c r="C41" s="214"/>
+      <c r="D41" s="215"/>
+      <c r="E41" s="211"/>
+      <c r="F41" s="217"/>
       <c r="G41" s="39"/>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -6554,9 +6554,9 @@
       <c r="BC41" s="20"/>
       <c r="BD41" s="69"/>
       <c r="BE41" s="69"/>
-      <c r="BF41" s="245"/>
-      <c r="BG41" s="245"/>
-      <c r="BH41" s="245"/>
+      <c r="BF41" s="139"/>
+      <c r="BG41" s="139"/>
+      <c r="BH41" s="139"/>
       <c r="BI41" s="14"/>
       <c r="BJ41" s="20"/>
       <c r="BK41" s="69"/>
@@ -6587,17 +6587,63 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="C32:D33"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B24:B37"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="C14:D15"/>
     <mergeCell ref="E14:E15"/>
@@ -6614,63 +6660,17 @@
     <mergeCell ref="C12:D13"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B24:B37"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -6706,54 +6706,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="204" t="s">
+      <c r="B1" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="207" t="s">
+      <c r="C1" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="208"/>
-      <c r="E1" s="213" t="s">
+      <c r="D1" s="150"/>
+      <c r="E1" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="215" t="s">
+      <c r="F1" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="198"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="199"/>
-      <c r="O1" s="199"/>
-      <c r="P1" s="199"/>
-      <c r="Q1" s="199"/>
-      <c r="R1" s="199"/>
-      <c r="S1" s="199"/>
-      <c r="T1" s="199"/>
-      <c r="U1" s="199"/>
-      <c r="V1" s="199"/>
-      <c r="W1" s="199"/>
-      <c r="X1" s="199"/>
-      <c r="Y1" s="199"/>
-      <c r="Z1" s="199"/>
-      <c r="AA1" s="199"/>
-      <c r="AB1" s="199"/>
-      <c r="AC1" s="199"/>
-      <c r="AD1" s="200"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="142"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="202"/>
-      <c r="B2" s="205"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="216"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="158"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -6828,12 +6828,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="203"/>
-      <c r="B3" s="206"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="217"/>
+      <c r="A3" s="145"/>
+      <c r="B3" s="148"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="159"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -6908,20 +6908,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="193">
+      <c r="A4" s="160">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="195"/>
-      <c r="E4" s="224" t="s">
+      <c r="D4" s="163"/>
+      <c r="E4" s="238" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="196"/>
+      <c r="F4" s="168"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -6944,20 +6944,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="225" t="s">
+      <c r="AC4" s="239" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="219" t="s">
+      <c r="AD4" s="233" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="163"/>
+      <c r="A5" s="161"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="160"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="197"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="165"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="169"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -6980,22 +6980,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="226"/>
-      <c r="AD5" s="220"/>
+      <c r="AC5" s="240"/>
+      <c r="AD5" s="234"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="149">
+      <c r="A6" s="170">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="157" t="s">
+      <c r="C6" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="158"/>
-      <c r="E6" s="222" t="s">
+      <c r="D6" s="179"/>
+      <c r="E6" s="236" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="189"/>
+      <c r="F6" s="183"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -7018,16 +7018,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="226"/>
-      <c r="AD6" s="220"/>
+      <c r="AC6" s="240"/>
+      <c r="AD6" s="234"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="163"/>
+      <c r="A7" s="161"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="190"/>
+      <c r="C7" s="180"/>
+      <c r="D7" s="181"/>
+      <c r="E7" s="237"/>
+      <c r="F7" s="184"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -7050,24 +7050,24 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="226"/>
-      <c r="AD7" s="220"/>
+      <c r="AC7" s="240"/>
+      <c r="AD7" s="234"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="228">
+      <c r="A8" s="222">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="230" t="s">
+      <c r="C8" s="242" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="231"/>
-      <c r="E8" s="232" t="s">
+      <c r="D8" s="243"/>
+      <c r="E8" s="244" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="178"/>
+      <c r="F8" s="195"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -7090,16 +7090,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="226"/>
-      <c r="AD8" s="220"/>
+      <c r="AC8" s="240"/>
+      <c r="AD8" s="234"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="229"/>
+      <c r="A9" s="223"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="191"/>
-      <c r="D9" s="192"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="177"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="E9" s="228"/>
+      <c r="F9" s="196"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -7122,24 +7122,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="226"/>
-      <c r="AD9" s="220"/>
+      <c r="AC9" s="240"/>
+      <c r="AD9" s="234"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="234">
+      <c r="A10" s="231">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="184" t="s">
+      <c r="C10" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="185"/>
-      <c r="E10" s="235" t="s">
+      <c r="D10" s="172"/>
+      <c r="E10" s="230" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="183"/>
+      <c r="F10" s="176"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -7162,16 +7162,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="226"/>
-      <c r="AD10" s="220"/>
+      <c r="AC10" s="240"/>
+      <c r="AD10" s="234"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="229"/>
+      <c r="A11" s="223"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="187"/>
-      <c r="E11" s="236"/>
-      <c r="F11" s="174"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="174"/>
+      <c r="E11" s="226"/>
+      <c r="F11" s="177"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -7194,22 +7194,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="226"/>
-      <c r="AD11" s="220"/>
+      <c r="AC11" s="240"/>
+      <c r="AD11" s="234"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="228">
+      <c r="A12" s="222">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="157" t="s">
+      <c r="C12" s="178" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="158"/>
-      <c r="E12" s="237" t="s">
+      <c r="D12" s="179"/>
+      <c r="E12" s="232" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="173"/>
+      <c r="F12" s="192"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7232,16 +7232,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="226"/>
-      <c r="AD12" s="220"/>
+      <c r="AC12" s="240"/>
+      <c r="AD12" s="234"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="234"/>
+      <c r="A13" s="231"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="182"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="183"/>
+      <c r="C13" s="189"/>
+      <c r="D13" s="190"/>
+      <c r="E13" s="230"/>
+      <c r="F13" s="176"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7264,24 +7264,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="226"/>
-      <c r="AD13" s="220"/>
+      <c r="AC13" s="240"/>
+      <c r="AD13" s="234"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="238">
+      <c r="A14" s="227">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="143" t="s">
+      <c r="C14" s="193" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="239" t="s">
+      <c r="D14" s="194"/>
+      <c r="E14" s="229" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="178"/>
+      <c r="F14" s="195"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7304,16 +7304,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="226"/>
-      <c r="AD14" s="220"/>
+      <c r="AC14" s="240"/>
+      <c r="AD14" s="234"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="238"/>
+      <c r="A15" s="227"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="159"/>
-      <c r="D15" s="160"/>
-      <c r="E15" s="236"/>
-      <c r="F15" s="174"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="165"/>
+      <c r="E15" s="226"/>
+      <c r="F15" s="177"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7336,22 +7336,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="226"/>
-      <c r="AD15" s="220"/>
+      <c r="AC15" s="240"/>
+      <c r="AD15" s="234"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="238">
+      <c r="A16" s="227">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="157" t="s">
+      <c r="C16" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="158"/>
-      <c r="E16" s="240" t="s">
+      <c r="D16" s="179"/>
+      <c r="E16" s="225" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="173"/>
+      <c r="F16" s="192"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7374,16 +7374,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="226"/>
-      <c r="AD16" s="220"/>
+      <c r="AC16" s="240"/>
+      <c r="AD16" s="234"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="238"/>
+      <c r="A17" s="227"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="159"/>
-      <c r="D17" s="160"/>
-      <c r="E17" s="236"/>
-      <c r="F17" s="174"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="226"/>
+      <c r="F17" s="177"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7406,22 +7406,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="226"/>
-      <c r="AD17" s="220"/>
+      <c r="AC17" s="240"/>
+      <c r="AD17" s="234"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="238">
+      <c r="A18" s="227">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="157" t="s">
+      <c r="C18" s="178" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="158"/>
-      <c r="E18" s="240" t="s">
+      <c r="D18" s="179"/>
+      <c r="E18" s="225" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="173"/>
+      <c r="F18" s="192"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7444,16 +7444,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="226"/>
-      <c r="AD18" s="220"/>
+      <c r="AC18" s="240"/>
+      <c r="AD18" s="234"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="238"/>
+      <c r="A19" s="227"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="233"/>
-      <c r="F19" s="177"/>
+      <c r="C19" s="180"/>
+      <c r="D19" s="181"/>
+      <c r="E19" s="228"/>
+      <c r="F19" s="196"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7476,24 +7476,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="226"/>
-      <c r="AD19" s="220"/>
+      <c r="AC19" s="240"/>
+      <c r="AD19" s="234"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="228">
+      <c r="A20" s="222">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="143" t="s">
+      <c r="C20" s="193" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="144"/>
-      <c r="E20" s="239" t="s">
+      <c r="D20" s="194"/>
+      <c r="E20" s="229" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="178"/>
+      <c r="F20" s="195"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -7516,18 +7516,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="226"/>
-      <c r="AD20" s="220"/>
+      <c r="AC20" s="240"/>
+      <c r="AD20" s="234"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="229"/>
+      <c r="A21" s="223"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="159"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="236"/>
-      <c r="F21" s="174"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="226"/>
+      <c r="F21" s="177"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -7550,22 +7550,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="226"/>
-      <c r="AD21" s="220"/>
+      <c r="AC21" s="240"/>
+      <c r="AD21" s="234"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="228">
+      <c r="A22" s="222">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="241" t="s">
+      <c r="C22" s="224" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="158"/>
-      <c r="E22" s="240" t="s">
+      <c r="D22" s="179"/>
+      <c r="E22" s="225" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="173"/>
+      <c r="F22" s="192"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -7588,16 +7588,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="226"/>
-      <c r="AD22" s="220"/>
+      <c r="AC22" s="240"/>
+      <c r="AD22" s="234"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="229"/>
+      <c r="A23" s="223"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="159"/>
-      <c r="D23" s="160"/>
-      <c r="E23" s="236"/>
-      <c r="F23" s="174"/>
+      <c r="C23" s="164"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="226"/>
+      <c r="F23" s="177"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -7620,22 +7620,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="226"/>
-      <c r="AD23" s="220"/>
+      <c r="AC23" s="240"/>
+      <c r="AD23" s="234"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="228">
+      <c r="A24" s="222">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="241" t="s">
+      <c r="C24" s="224" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="158"/>
-      <c r="E24" s="240" t="s">
+      <c r="D24" s="179"/>
+      <c r="E24" s="225" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="173"/>
+      <c r="F24" s="192"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -7658,16 +7658,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="226"/>
-      <c r="AD24" s="220"/>
+      <c r="AC24" s="240"/>
+      <c r="AD24" s="234"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="229"/>
+      <c r="A25" s="223"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="160"/>
-      <c r="E25" s="236"/>
-      <c r="F25" s="177"/>
+      <c r="C25" s="164"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="226"/>
+      <c r="F25" s="196"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -7690,24 +7690,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="226"/>
-      <c r="AD25" s="220"/>
+      <c r="AC25" s="240"/>
+      <c r="AD25" s="234"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="149">
+      <c r="A26" s="170">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="164" t="s">
+      <c r="C26" s="202" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="165"/>
-      <c r="E26" s="242" t="s">
+      <c r="D26" s="203"/>
+      <c r="E26" s="219" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="169"/>
+      <c r="F26" s="206"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -7730,16 +7730,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="226"/>
-      <c r="AD26" s="220"/>
+      <c r="AC26" s="240"/>
+      <c r="AD26" s="234"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="163"/>
+      <c r="A27" s="161"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="166"/>
-      <c r="D27" s="167"/>
-      <c r="E27" s="243"/>
-      <c r="F27" s="170"/>
+      <c r="C27" s="204"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="220"/>
+      <c r="F27" s="207"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -7762,24 +7762,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="226"/>
-      <c r="AD27" s="220"/>
+      <c r="AC27" s="240"/>
+      <c r="AD27" s="234"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="149">
+      <c r="A28" s="170">
         <v>14</v>
       </c>
-      <c r="B28" s="141" t="s">
+      <c r="B28" s="212" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="143" t="s">
+      <c r="C28" s="193" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="144"/>
-      <c r="E28" s="141" t="s">
+      <c r="D28" s="194"/>
+      <c r="E28" s="212" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="147"/>
+      <c r="F28" s="216"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -7802,16 +7802,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="226"/>
-      <c r="AD28" s="220"/>
+      <c r="AC28" s="240"/>
+      <c r="AD28" s="234"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="244"/>
-      <c r="B29" s="142"/>
-      <c r="C29" s="145"/>
-      <c r="D29" s="146"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="148"/>
+      <c r="A29" s="221"/>
+      <c r="B29" s="213"/>
+      <c r="C29" s="214"/>
+      <c r="D29" s="215"/>
+      <c r="E29" s="213"/>
+      <c r="F29" s="217"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -7834,8 +7834,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="227"/>
-      <c r="AD29" s="221"/>
+      <c r="AC29" s="241"/>
+      <c r="AD29" s="235"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -7855,45 +7855,12 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -7910,12 +7877,45 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
